--- a/docs/xlsx/jobs-2026-09-23.xlsx
+++ b/docs/xlsx/jobs-2026-09-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="584">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1741 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>AmeriCorps Community Educator</t>
+  </si>
+  <si>
+    <t>The Wild Center</t>
+  </si>
+  <si>
+    <t>Tupper Lake, NY</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$1,700 per month</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-americorps-community-educator-tupper-lake-new-york/4536343861</t>
+  </si>
+  <si>
+    <t>Assistant Professor in Stock Assessment</t>
+  </si>
+  <si>
+    <t>Michigan State University</t>
+  </si>
+  <si>
+    <t>East Lansing, MI</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>$100,000 - $125,000 per year</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-professor-in-stock-assessment-east-lansing-michigan/7792924397</t>
+  </si>
+  <si>
+    <t>Camp and Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Chimfunshi Wildlife Orphanage Trust</t>
+  </si>
+  <si>
+    <t>Chingola, Africa</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Depending on qualifications and experience</t>
+  </si>
+  <si>
+    <t>admin-leadership-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-camp-and-operations-coordinator-chingola-africa/7560896580</t>
+  </si>
+  <si>
+    <t>Coastal Advocate – MID COAST</t>
+  </si>
+  <si>
+    <t>One Hundred Miles</t>
+  </si>
+  <si>
+    <t>Darien, GA</t>
+  </si>
+  <si>
+    <t>$50,000 - $60,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-marine-biology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-coastal-advocate--mid-coast-brunswick-georgia/6167315915</t>
+  </si>
+  <si>
+    <t>Coastal Planning and Policy Strategist</t>
+  </si>
+  <si>
+    <t>Savannah, GA</t>
+  </si>
+  <si>
+    <t>$50,000 - $65,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-coastal-planning-and-policy-strategist-brunswick-georgia/9328801578</t>
+  </si>
+  <si>
+    <t>Conservation Analytics Biologist</t>
+  </si>
+  <si>
+    <t>Catalina Island Conservancy</t>
+  </si>
+  <si>
+    <t>Long Beach, California, United States, CA</t>
+  </si>
+  <si>
+    <t>$80 - $86 per year</t>
+  </si>
+  <si>
+    <t>ecology-wildlife-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-analytics-biologist-long-beach-california-united-states-california/7651072483</t>
+  </si>
+  <si>
+    <t>Conservation Assistant</t>
+  </si>
+  <si>
+    <t>Windham County Natural Resources Conservation District</t>
+  </si>
+  <si>
+    <t>Brattleboro, VT</t>
+  </si>
+  <si>
+    <t>$31,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-assistant-brattleboro-vermont/4050327292</t>
+  </si>
+  <si>
+    <t>Construction Manager</t>
+  </si>
+  <si>
+    <t>Wildlands Engineering</t>
+  </si>
+  <si>
+    <t>Raleigh, NC</t>
+  </si>
+  <si>
+    <t>$75,000 - $115,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-construction-manager-raleigh-north-carolina/9400046324</t>
+  </si>
+  <si>
+    <t>Crew Lead 1</t>
+  </si>
+  <si>
+    <t>Missouri Native Stewardship Services</t>
+  </si>
+  <si>
+    <t>St. Louis, MO</t>
+  </si>
+  <si>
+    <t>$26 - $28 per hour</t>
+  </si>
+  <si>
+    <t>botany-general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-crew-lead-1-st-louis-missouri/9823373261</t>
+  </si>
+  <si>
+    <t>Environmental Review and Permitting Specialist</t>
+  </si>
+  <si>
+    <t>CC Environment &amp; Planning</t>
+  </si>
+  <si>
+    <t>Batavia, NY</t>
+  </si>
+  <si>
+    <t>$85,000 - $95,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-review-and-permitting-specialist-batavia-new-york/7608241854</t>
+  </si>
+  <si>
+    <t>EPA Fellowship on Alternatives for Assessing Toxicity of Environmental Contaminants to Aquatic Organisms</t>
+  </si>
+  <si>
+    <t>U.S. Environmental Protection Agency (EPA)</t>
+  </si>
+  <si>
+    <t>Cincinnati, OH</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>The participant will receive a monthly stipend commensurate with educational level and experience.</t>
+  </si>
+  <si>
+    <t>ecology-fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-epa-fellowship-on-alternatives-for-assessing-toxicity-of-environmental-contaminants-to-aquatic-organisms-cincinnati-ohio/5318343992</t>
+  </si>
+  <si>
+    <t>Executive Director of Harbor Branch Oceanographic Institute</t>
+  </si>
+  <si>
+    <t>Florida Atlantic University</t>
+  </si>
+  <si>
+    <t>Fort Pierce, FL</t>
+  </si>
+  <si>
+    <t>Salary Commensurate with Experience</t>
+  </si>
+  <si>
+    <t>admin-leadership-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-of-harbor-branch-oceanographic-institute-fort-pierce-florida/2848608657</t>
+  </si>
+  <si>
+    <t>Faculty Position, Marine Science</t>
+  </si>
+  <si>
+    <t>Dauphin Island Sea Lab</t>
+  </si>
+  <si>
+    <t>Dauphin Island, AL</t>
+  </si>
+  <si>
+    <t>Negotiable</t>
+  </si>
+  <si>
+    <t>marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-faculty-position-marine-science-dauphin-island-alabama/1357753760</t>
+  </si>
+  <si>
+    <t>Field Technician</t>
+  </si>
+  <si>
+    <t>Southeastern Grasslands Institute at Austin Peay State University</t>
+  </si>
+  <si>
+    <t>Chattanooga, TN</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$20 per hour</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-technician-chattanooga-tennessee/5957919689</t>
+  </si>
+  <si>
+    <t>Fish Culturist</t>
+  </si>
+  <si>
+    <t>Wyoming Game &amp; Fish</t>
+  </si>
+  <si>
+    <t>Cheyenne, WY</t>
+  </si>
+  <si>
+    <t>$5,158.40 - $5,730.40 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fish-culturist-cheyenne-wyoming/5430798121</t>
+  </si>
+  <si>
+    <t>Fisheries Biologist - Advanced Field Operations and Data Modernization</t>
+  </si>
+  <si>
+    <t>Astor Environmental LLC</t>
+  </si>
+  <si>
+    <t>Hammond, OR</t>
+  </si>
+  <si>
+    <t>$37 - $42 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fisheries-biologist---advanced-field-operations-and-data-modernization-hammond-oregon/8844455757</t>
+  </si>
+  <si>
+    <t>Forest Conservation Coordinator | South Tri-State Position</t>
+  </si>
+  <si>
+    <t>Ruffed Grouse Society</t>
+  </si>
+  <si>
+    <t>Asheville, NC</t>
+  </si>
+  <si>
+    <t>$60,000 - $84,000 per year</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forest-conservation-coordinator--south-tri-state-position-asheville-north-carolina/1678671143</t>
+  </si>
+  <si>
+    <t>Forest Wildlife Specialist - Tennessee Private Lands, 2-Year Term</t>
+  </si>
+  <si>
+    <t>Ruffed Grouse Society &amp; American Woodcock Society</t>
+  </si>
+  <si>
+    <t>Knoxville, GA</t>
+  </si>
+  <si>
+    <t>$44,000 - $68,000 per year</t>
+  </si>
+  <si>
+    <t>forestry-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forest-wildlife-specialist---tennessee-private-lands-2-year-term-knoxville-georgia/2931698859</t>
+  </si>
+  <si>
+    <t>Habitat Restoration Technician</t>
+  </si>
+  <si>
+    <t>Sound Salmon Solutions</t>
+  </si>
+  <si>
+    <t>Mukilteo, WA</t>
+  </si>
+  <si>
+    <t>$18 - $19 per hour</t>
+  </si>
+  <si>
+    <t>hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-habitat-restoration-technician-mukilteo-washington/5946495579</t>
+  </si>
+  <si>
+    <t>Inside Grass Seed Salesperson</t>
+  </si>
+  <si>
+    <t>Clearwater Seed/ Millborn Seeds</t>
+  </si>
+  <si>
+    <t>Spokane, WA</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-inside-grass-seed-salesperson-spokane-washington/9943208901</t>
+  </si>
+  <si>
+    <t>Invasive Species Specialist - Individual Placement</t>
+  </si>
+  <si>
+    <t>Conservation Corps New Mexico</t>
+  </si>
+  <si>
+    <t>Liberty, TX</t>
+  </si>
+  <si>
+    <t>$640 per week</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-invasive-species-specialist---individual-placement-liberty-texas/2994697599</t>
+  </si>
+  <si>
+    <t>Jr. Legal Assistant - Real Property Specialist</t>
+  </si>
+  <si>
+    <t>Trust for Public Land</t>
+  </si>
+  <si>
+    <t>Tallahassee, FL</t>
+  </si>
+  <si>
+    <t>$51,462 - $69,864 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-land-trust-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-jr-legal-assistant---real-property-specialist-tallahassee-florida/8362718380</t>
+  </si>
+  <si>
+    <t>Land Management Technician</t>
+  </si>
+  <si>
+    <t>Endangered Habitats Conservancy</t>
+  </si>
+  <si>
+    <t>San Diego, CA</t>
+  </si>
+  <si>
+    <t>$45,000 - $50,000 per year</t>
+  </si>
+  <si>
+    <t>land-trust-outdoor-recreation-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-land-management-technician-san-diego-california/1496048608</t>
+  </si>
+  <si>
+    <t>Land Manager- Menomonee Valley</t>
+  </si>
+  <si>
+    <t>Urban Ecology Center</t>
+  </si>
+  <si>
+    <t>Milwaukee, WI</t>
+  </si>
+  <si>
+    <t>$46,000 - $48,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-land-manager--menomonee-valley-milwaukee-wisconsin/8433386642</t>
+  </si>
+  <si>
+    <t>Motus Technical Specialist</t>
+  </si>
+  <si>
+    <t>American Bird Conservancy</t>
+  </si>
+  <si>
+    <t>Remote; priority is location within lower Mississippi Valley, Remote</t>
+  </si>
+  <si>
+    <t>Estimated at $50,460 -$55,882*; Based on experience</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-motus-technical-specialist-remote-priority-is-location-within-lower-mississippi-valley-remote/5133316186</t>
+  </si>
+  <si>
+    <t>Museum Technician (NPS, George Washington Memorial Parkway)</t>
+  </si>
+  <si>
+    <t>Great Basin Institute</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>$22.33 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-museum-technician-nps-george-washington-memorial-parkway-washington-dc/4955266070</t>
+  </si>
+  <si>
+    <t>Natural Resource Specialist</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Loomis, WA</t>
+  </si>
+  <si>
+    <t>$4,004 - $5,376 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resource-specialist-loomis-washington/8905200852</t>
+  </si>
+  <si>
+    <t>Natural Resources Specialist I - II- III (Wildlife District I Biologist)</t>
+  </si>
+  <si>
+    <t>Texas Parks and Wildlife Department</t>
+  </si>
+  <si>
+    <t>Jeff Davis &amp; Reeves Counties, TX</t>
+  </si>
+  <si>
+    <t>$4,504.18 - $5,824.14 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-specialist-i---ii--iii-wildlife-district-i-biologist-jeff-davis--reeves-counties-texas/2547083405</t>
+  </si>
+  <si>
+    <t>Office &amp; Administrative Specialist, Senior</t>
+  </si>
+  <si>
+    <t>Minnesota Department of Natural Resources, Division of Forestry</t>
+  </si>
+  <si>
+    <t>Aitkin, MN</t>
+  </si>
+  <si>
+    <t>$22.62 - $30.62 / hourly; $47,230 - $63,934 / annually</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-office--administrative-specialist-senior-aitkin-minnesota/5231612487</t>
+  </si>
+  <si>
+    <t>Operations and Finance Director</t>
+  </si>
+  <si>
+    <t>Wilderness Workshop</t>
+  </si>
+  <si>
+    <t>Carbondale, CO</t>
+  </si>
+  <si>
+    <t>$79,500 - $114,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-operations-and-finance-director-carbondale-colorado/8219753132</t>
+  </si>
+  <si>
+    <t>Outdoor Education Instructor</t>
+  </si>
+  <si>
+    <t>Pali Institute</t>
+  </si>
+  <si>
+    <t>Running Springs, CA</t>
+  </si>
+  <si>
+    <t>Total Compensation Package from $1030-$1075 a week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-outdoor-education-instructor-running-springs-california/3776022738</t>
+  </si>
+  <si>
+    <t>Outdoor Educator</t>
+  </si>
+  <si>
+    <t>Camp Allen</t>
+  </si>
+  <si>
+    <t>Navasota, TX</t>
+  </si>
+  <si>
+    <t>$375 - $400 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-outdoor-educator-navasota-texas/9054911511</t>
+  </si>
+  <si>
+    <t>Prescribed Burn Association Coordinator</t>
+  </si>
+  <si>
+    <t>Pheasants Forever, Inc., and Quail Forever</t>
+  </si>
+  <si>
+    <t>Negotiable, central AR preferred, AR</t>
+  </si>
+  <si>
+    <t>Up to $55,000 (commensurate with knowledge, skills, and experience)</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-prescribed-burn-association-coordinator-negotiable-central-ar-preferred-arkansas/5622389206</t>
+  </si>
+  <si>
+    <t>Program Operations Associate, Conservation Innovation</t>
+  </si>
+  <si>
+    <t>Open Space Institute</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>$66,000 - $70,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-operations-associate-conservation-innovation-new-york-new-york/5108863950</t>
+  </si>
+  <si>
+    <t>Program Supervisor V (Public Hunting Coordinator)</t>
+  </si>
+  <si>
+    <t>Austin, TX</t>
+  </si>
+  <si>
+    <t>$7,694.42 per month</t>
+  </si>
+  <si>
+    <t>outdoor-recreation-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-supervisor-v-public-hunting-coordinator-austin-texas/4552835016</t>
+  </si>
+  <si>
+    <t>Southern California Regional Director</t>
+  </si>
+  <si>
+    <t>WRA Inc</t>
+  </si>
+  <si>
+    <t>Southern California, CA</t>
+  </si>
+  <si>
+    <t>$155,000 - $208,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-southern-california-regional-director-southern-california-california/4618802386</t>
+  </si>
+  <si>
+    <t>Staff Wildlife Rehabilitator</t>
+  </si>
+  <si>
+    <t>Rockfish Wildlife Sanctuary</t>
+  </si>
+  <si>
+    <t>Shipman, VA</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-staff-wildlife-rehabilitator-shipman-virginia/4885116627</t>
+  </si>
+  <si>
+    <t>Warehouse Associate</t>
+  </si>
+  <si>
+    <t>$19.50 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-warehouse-associate-spokane-washington/5593221721</t>
+  </si>
+  <si>
+    <t>Water Resources Regulatory Specialist</t>
+  </si>
+  <si>
+    <t>Capitol Region Watershed District</t>
+  </si>
+  <si>
+    <t>Saint Paul, MN</t>
+  </si>
+  <si>
+    <t>$59,628 - $89,506 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-resources-regulatory-specialist-saint-paul-minnesota/3451400503</t>
+  </si>
+  <si>
+    <t>Work Planner</t>
+  </si>
+  <si>
+    <t>ArborMetrics</t>
+  </si>
+  <si>
+    <t>Muskegon, MI</t>
+  </si>
+  <si>
+    <t>$23 - $26 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-work-planner-muskegon-michigan/8154284012</t>
+  </si>
+  <si>
+    <t>Accounting Manager</t>
+  </si>
+  <si>
+    <t>The Posse Foundation, Inc.</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/85859014ee2c431c99a6b97da0a604bc-accounting-manager-the-posse-foundation-inc-new-york</t>
+  </si>
+  <si>
+    <t>Administrative &amp; Communications Coordinator</t>
+  </si>
+  <si>
+    <t>Glendale Baptist Church</t>
+  </si>
+  <si>
+    <t>Nashville, Tennessee</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 21.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/41eda023c9bf4c189a496895fb9f106a-administrative-communications-coordinator-glendale-baptist-church-nashville</t>
+  </si>
+  <si>
+    <t>Assistant, Associate or Full Professor in Community Psychology</t>
+  </si>
+  <si>
+    <t>The American University in Cairo</t>
+  </si>
+  <si>
+    <t>Hewlett, New York</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/77b002b3c2614286a4ea790072d07f18-assistant-associate-or-full-professor-in-community-psychology-the-american-university-in-cairo-hewlett</t>
+  </si>
+  <si>
+    <t>Associate Director, Data Hub</t>
+  </si>
+  <si>
+    <t>Project Evident</t>
+  </si>
+  <si>
+    <t>Remote (Boston, Massachusetts)</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Philanthropy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a99ac586e8324e088a16bd3bac585a28-associate-director-data-hub-project-evident-boston</t>
+  </si>
+  <si>
+    <t>Chief Financial and Operations Officer</t>
+  </si>
+  <si>
+    <t>Acquire Talent Partners</t>
+  </si>
+  <si>
+    <t>Wilton, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/bed6162fa0cd44949c3e63fef64a22e8-chief-financial-and-operations-officer-acquire-talent-partners-wilton</t>
+  </si>
+  <si>
+    <t>Chief Legal Officer</t>
+  </si>
+  <si>
+    <t>Justice at Work PA (Formerly Friends of Farmworkers)</t>
+  </si>
+  <si>
+    <t>Pittsburgh, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Economic Development, Family, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/519c16af9bf647629fc227d360e4abf4-chief-legal-officer-justice-at-work-pa-formerly-friends-of-farmworkers-pittsburgh</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c50e4ef21b34eeb90cb5f0857f72731-chief-legal-officer-justice-at-work-pa-formerly-friends-of-farmworkers-philadelphia</t>
+  </si>
+  <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/efc7bffbcfca41318c1589a41be101de-chief-operating-officer-justice-at-work-pa-formerly-friends-of-farmworkers-philadelphia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d11702f60044bdd90fe3d52141edf32-chief-operating-officer-justice-at-work-pa-formerly-friends-of-farmworkers-pittsburgh</t>
+  </si>
+  <si>
+    <t>Oakland Promise</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 200000.00 - 240000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7ad10fb5b9fe47c8848b4e1c7d68d378-chief-operating-officer-oakland-promise-oakland</t>
+  </si>
+  <si>
+    <t>Clinical Program Coordinator</t>
+  </si>
+  <si>
+    <t>Gateway Arts/Vinfen</t>
+  </si>
+  <si>
+    <t>Brookline, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 42000.00 - 48000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/946b0b132a14425c9ff7a6c846b00fce-clinical-program-coordinator-gateway-artsvinfen-brookline</t>
+  </si>
+  <si>
+    <t>Clinician - Collective RAPP (Queens)</t>
+  </si>
+  <si>
+    <t>Day One NY</t>
+  </si>
+  <si>
+    <t>USD 74500.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/adf9cdfe38cf430cb161871b46556451-clinician-collective-rapp-queens-day-one-ny-new-york</t>
+  </si>
+  <si>
+    <t>Community Development Manager</t>
+  </si>
+  <si>
+    <t>Parkinson's Foundation</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Community Development, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87354e3c76684566972165474c60018e-community-development-manager-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>Food Lifeline</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/787deeef13e0455d9d0a65f5426093d2-controller-food-lifeline-seattle</t>
+  </si>
+  <si>
+    <t>Creative District Program Director</t>
+  </si>
+  <si>
+    <t>Woodinville Arts Alliance</t>
+  </si>
+  <si>
+    <t>Woodinville, Washington</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/469cdf0c6fb44004b4f92a1134c378f3-creative-district-program-director-woodinville-arts-alliance-woodinville</t>
+  </si>
+  <si>
+    <t>CUNY Office Assistant (Academic Affairs)</t>
+  </si>
+  <si>
+    <t>City University of New York (CUNY) School of Law</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 36700.00 - 41472.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cecb886a70ac493f984aa3d556c00653-cuny-office-assistant-academic-affairs-city-university-of-new-york-cuny-school-of-law-queens-county</t>
+  </si>
+  <si>
+    <t>Development Assistant</t>
+  </si>
+  <si>
+    <t>The Conservation Law Foundation</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 56000.00 - 60500.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f864f1b4c3d3499dadd608759d10acf9-development-assistant-the-conservation-law-foundation-boston</t>
+  </si>
+  <si>
+    <t>Direct Support Professional</t>
+  </si>
+  <si>
+    <t>WeAchieve Inc</t>
+  </si>
+  <si>
+    <t>Silver Spring, Maryland</t>
+  </si>
+  <si>
+    <t>USD 18.40 - 18.40/hour</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0595f1ac12524c81946cd3230d52fdfd-direct-support-professional-weachieve-inc-silver-spring</t>
+  </si>
+  <si>
+    <t>Director of Community Strategy</t>
+  </si>
+  <si>
+    <t>North10 Philadelphia</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Urban Areas, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8076d1df3854cc2a6811868e9b4510b-director-of-community-strategy-north10-philadelphia-philadelphia</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Sephardic Community Center</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/574617ca8ac84083b17d445b75948018-director-of-development-sephardic-community-center-brooklyn</t>
+  </si>
+  <si>
+    <t>Director of Leadership Giving</t>
+  </si>
+  <si>
+    <t>The Connecticut Mirror</t>
+  </si>
+  <si>
+    <t>Hartford, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 92000.00 - 106000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0bcb4c57d12247cca6bb1b00356bacb5-director-of-leadership-giving-the-connecticut-mirror-hartford</t>
+  </si>
+  <si>
+    <t>Director of Membership</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96edf4d439e146128c315e55aaeeb850-director-of-membership-sephardic-community-center-brooklyn</t>
+  </si>
+  <si>
+    <t>Director of Technology</t>
+  </si>
+  <si>
+    <t>The Gilder Lehrman Institute of American History</t>
+  </si>
+  <si>
+    <t>USD 185000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d5508649bc5043ff95003ad14a5a3102-director-of-technology-the-gilder-lehrman-institute-of-american-history-new-york</t>
+  </si>
+  <si>
+    <t>Director, Growth &amp; External Relations</t>
+  </si>
+  <si>
+    <t>trubel&amp;co</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/66ffdd87adfa468792bcea6f9c206b8b-director-growth-external-relations-trubelco-dover</t>
+  </si>
+  <si>
+    <t>Director, Inclusive Entrepreneurship</t>
+  </si>
+  <si>
+    <t>Candide Group</t>
+  </si>
+  <si>
+    <t>USD 165000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>Entrepreneurship, Race Ethnicity, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/ffcb91da65284006917fd352028a1fe4-director-inclusive-entrepreneurship-candide-group-oakland</t>
+  </si>
+  <si>
+    <t>Dog Behavior Specialist</t>
+  </si>
+  <si>
+    <t>Orphans of the Storm</t>
+  </si>
+  <si>
+    <t>Riverwoods, Illinois</t>
+  </si>
+  <si>
+    <t>USD 40000.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c5b8d9bbae814ead89236eeb288dc36e-dog-behavior-specialist-orphans-of-the-storm-riverwoods</t>
+  </si>
+  <si>
+    <t>Donor Relations Coordinator, Miami</t>
+  </si>
+  <si>
+    <t>Miami, Florida</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/95806c1dbd5747b1bcb7f75ea12c2e24-donor-relations-coordinator-miami-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Donor Relations DATA ENTRY Coordinator, New York</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d0f153eabe24c358e43fc81b1ef7cf0-donor-relations-data-entry-coordinator-new-york-parkinsons-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Editorial Manager</t>
+  </si>
+  <si>
+    <t>Human Rights Foundation</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8bf1b9cf60ea4dd9a20d75c86c62b2d6-editorial-manager-human-rights-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Environmental Analyst</t>
+  </si>
+  <si>
+    <t>NESCAUM</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Energy, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/91ca6b699329428bb0fbf1238c16c5c1-environmental-analyst-nescaum-boston</t>
+  </si>
+  <si>
+    <t>Environmental Justice Attorney (Maine)</t>
+  </si>
+  <si>
+    <t>Portland, Maine</t>
+  </si>
+  <si>
+    <t>USD 85000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b7cdc44f06a24ba58a4fb3db14dadbad-environmental-justice-attorney-maine-the-conservation-law-foundation-portland</t>
+  </si>
+  <si>
+    <t>ETSU GLOBAL PRIMARY CARE FELLOWSHIP | Non-ACGME Post-Residency Fellowship</t>
+  </si>
+  <si>
+    <t>Hillside Health Care</t>
+  </si>
+  <si>
+    <t>Eldridgeville, Toledo District, BZ</t>
+  </si>
+  <si>
+    <t>Health Medicine, Women, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/78089408c99946d6b3cc4961b00098f9-etsu-global-primary-care-fellowship-non-acgme-post-residency-fellowship-hillside-health-care-eldridgeville</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Castle Square Tenants Organization</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ddf37ec244754ca180fda3c0a6c22cb8-executive-director-castle-square-tenants-organization-boston</t>
+  </si>
+  <si>
+    <t>Rolling Harvest Food Rescue</t>
+  </si>
+  <si>
+    <t>Lumberville, PA</t>
+  </si>
+  <si>
+    <t>Agriculture, Environment, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a9d2217aa9ee48f1a3eea04c5d0d9779-executive-director-rolling-harvest-food-rescue-lumberville</t>
+  </si>
+  <si>
+    <t>Facilities Manager</t>
+  </si>
+  <si>
+    <t>The Aldrich Contemporary Art Museum</t>
+  </si>
+  <si>
+    <t>Ridgefield, CT</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/219bd6d1ac2d40188533c08713c84db0-facilities-manager-the-aldrich-contemporary-art-museum-ridgefield</t>
+  </si>
+  <si>
+    <t>Finance and Operations Manager</t>
+  </si>
+  <si>
+    <t>Partners for a Hunger-Free Oregon</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/482ade3363f4431b803ca281ac3342c9-finance-and-operations-manager-partners-for-a-hunger-free-oregon-portland</t>
+  </si>
+  <si>
+    <t>International Director</t>
+  </si>
+  <si>
+    <t>Swift Sports Organisation</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 100.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f13ff62c7fef4708abe84491b720cc93-international-director-swift-sports-organisation-kampala</t>
+  </si>
+  <si>
+    <t>IT Support Specialist: Electronic Investigative Support Group, Rochester (6460)</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>Rochester, New York</t>
+  </si>
+  <si>
+    <t>USD 86686.00 - 86686.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/1ad2ecea3aab4a7f8a62b4d5f6303a29-it-support-specialist-electronic-investigative-support-group-rochester-6460-new-york-state-office-of-the-attorney-general-rochester</t>
+  </si>
+  <si>
+    <t>IT Support Specialist: Medicaid Fraud Control Unit (6459)</t>
+  </si>
+  <si>
+    <t>USD 90836.00 - 90836.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/951aca06cb2c4ff984bcb028f8932433-it-support-specialist-medicaid-fraud-control-unit-6459-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>Literacy Specialist</t>
+  </si>
+  <si>
+    <t>Masa</t>
+  </si>
+  <si>
+    <t>Bronx, NY</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87d93e700d4641e9877f607d99ddeefc-literacy-specialist-masa-bronx</t>
+  </si>
+  <si>
+    <t>Major Gifts Manager</t>
+  </si>
+  <si>
+    <t>States Newsroom</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bf2535faa5aa49ad80f3f7acfbcd4628-major-gifts-manager-states-newsroom-chapel-hill</t>
+  </si>
+  <si>
+    <t>Meetings and Events Manager</t>
+  </si>
+  <si>
+    <t>National Asian Pacific American Bar Association</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5026168dcde4412c860bd330870acdf4-meetings-and-events-manager-national-asian-pacific-american-bar-association-washington</t>
+  </si>
+  <si>
+    <t>Membership Manager</t>
+  </si>
+  <si>
+    <t>Stepping Stones Museum for Children</t>
+  </si>
+  <si>
+    <t>Norwalk, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d087327b8ea340cc86ca221381a6bc30-membership-manager-stepping-stones-museum-for-children-norwalk</t>
+  </si>
+  <si>
+    <t>Non-Profit Bookkeeper</t>
+  </si>
+  <si>
+    <t>Limitless Horizons Ixil</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4f8166a8ade042309745ecd53a040ea0-non-profit-bookkeeper-limitless-horizons-ixil-canton-ilom-chajul</t>
+  </si>
+  <si>
+    <t>Ocean Staff Attorney (Term-Limited)</t>
+  </si>
+  <si>
+    <t>Montpelier, Vermont</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>Community Development, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f0046c7febe44c8c87a08ae8fe4b2dc1-ocean-staff-attorney-term-limited-the-conservation-law-foundation-montpelier</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e97945b994624d5496cefa4bb2915ddd-ocean-staff-attorney-term-limited-the-conservation-law-foundation-boston</t>
+  </si>
+  <si>
+    <t>Providence, Rhode Island</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ccaa6e616bef49c0bc063f4131641ba9-ocean-staff-attorney-term-limited-the-conservation-law-foundation-providence</t>
+  </si>
+  <si>
+    <t>New Haven, Connecticut</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca55c09ca6fe45c7a56c76ca3c30f79c-ocean-staff-attorney-term-limited-the-conservation-law-foundation-new-haven</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/85d4b3ae23824263b2739e8db6362602-ocean-staff-attorney-term-limited-the-conservation-law-foundation-portland</t>
+  </si>
+  <si>
+    <t>Concord, New Hampshire</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/49dd0a3b55a34a9d93eade021eb72cc6-ocean-staff-attorney-term-limited-the-conservation-law-foundation-concord</t>
+  </si>
+  <si>
+    <t>Office of Developmental Disabilities Ombuds Region 2 DD Ombuds</t>
+  </si>
+  <si>
+    <t>Disability Rights Washington</t>
+  </si>
+  <si>
+    <t>USD 73759.00 - 81416.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f397bbefecb645559fa1a732cdded958-office-of-developmental-disabilities-ombuds-region-2-dd-ombuds-disability-rights-washington-seattle</t>
+  </si>
+  <si>
+    <t>Parent to Parent Coordinator</t>
+  </si>
+  <si>
+    <t>The Arc of King County</t>
+  </si>
+  <si>
+    <t>SeaTac, Washington</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Disability, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/378f1c0be41c4f1181f02d1c44eb406d-parent-to-parent-coordinator-the-arc-of-king-county-seatac</t>
+  </si>
+  <si>
+    <t>Physical Therapist in Belize (Volunteer)</t>
+  </si>
+  <si>
+    <t>USD 16000.00 - 18000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Disability, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ed05c38b3a0460f85192f27702b8101-physical-therapist-in-belize-volunteer-hillside-health-care-eldridgeville</t>
+  </si>
+  <si>
+    <t>PRIMARY STEM and Humanities positions in beach-jungle school in PUERTO RICO</t>
+  </si>
+  <si>
+    <t>PROEA - Pro Educacion y Ambiente</t>
+  </si>
+  <si>
+    <t>Rincón, Rincón, PR</t>
+  </si>
+  <si>
+    <t>USD 35000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca633ba38c594095868329a3e37504fb-primary-stem-and-humanities-positions-in-beach-jungle-school-in-puerto-rico-proea-pro-educacion-y-ambiente-rincon</t>
+  </si>
+  <si>
+    <t>Program Assistant</t>
+  </si>
+  <si>
+    <t>Project Citizenship</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ffa95358ebbf4cfcb5b5f508fe5dde49-program-assistant-project-citizenship-boston</t>
+  </si>
+  <si>
+    <t>Program Manager - Internships</t>
+  </si>
+  <si>
+    <t>PENCIL</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 66000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/25429480929e45a59abcb1d63dbda9e0-program-manager-internships-pencil-new-york</t>
+  </si>
+  <si>
+    <t>Program Manager, Live Programs</t>
+  </si>
+  <si>
+    <t>Constructive Dialogue Institute</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b18cb211748d48218636388f34750787-program-manager-live-programs-constructive-dialogue-institute-new-york</t>
+  </si>
+  <si>
+    <t>Project Assistant</t>
+  </si>
+  <si>
+    <t>COLLABORATING AGENCIES DISASTER RELIEF EFFORT</t>
+  </si>
+  <si>
+    <t>San Jose, California</t>
+  </si>
+  <si>
+    <t>USD 25.00/hour</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Seniors Retirement, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/68acd7f674a641c89edff7fcdd51c940-project-assistant-collaborating-agencies-disaster-relief-effort-san-jose</t>
+  </si>
+  <si>
+    <t>Project Manager (Temporary, Full-time)</t>
+  </si>
+  <si>
+    <t>National WIC Association</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 103000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2bb112490b4d446ba6b25a03ebb3dccc-project-manager-temporary-full-time-national-wic-association-washington</t>
+  </si>
+  <si>
+    <t>Psicóloga Institucional Hogar ADOLESCENTES ( es requisito viva en zona - EXCLUYENTE)</t>
+  </si>
+  <si>
+    <t>Hogar de Niños María Luisa</t>
+  </si>
+  <si>
+    <t>Villa Ballester, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Children Youth, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d12913d8bbaa44fbb2e634e75820835a-psicologa-institucional-hogar-adolescentes-es-requisito-viva-en-zona-excluyente-hogar-de-ninos-maria-luisa-villa-ballester</t>
+  </si>
+  <si>
+    <t>Resilience Corps Fellow</t>
+  </si>
+  <si>
+    <t>Greater Portland Council of Governments</t>
+  </si>
+  <si>
+    <t>USD 28000.00 - 28000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Energy, Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/d5fd005719df42c0b9059148f1a47a95-resilience-corps-fellow-greater-portland-council-of-governments-portland</t>
+  </si>
+  <si>
+    <t>Senior Accountant</t>
+  </si>
+  <si>
+    <t>NEIGHBORHOOD LEGAL SERVICES PROGRAM OF THE DISTRICT OF COLUMBIA</t>
+  </si>
+  <si>
+    <t>WASHINGTON, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 92000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6c1427bbbddd4fca837f0d8462f97aa9-senior-accountant-neighborhood-legal-services-program-of-the-district-of-columbia-washington</t>
+  </si>
+  <si>
+    <t>Service Coordinator</t>
+  </si>
+  <si>
+    <t>Phipps Houses</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bc33b9d005bc42a99d4e6216ba074bc5-service-coordinator-phipps-houses-new-york</t>
+  </si>
+  <si>
+    <t>Site Associate, GreenLight Fund Kansas City</t>
+  </si>
+  <si>
+    <t>GreenLight Fund</t>
+  </si>
+  <si>
+    <t>Kansas City, Missouri</t>
+  </si>
+  <si>
+    <t>USD 69860.00 - 72860.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/16b3fe8ba055424c9902883e40ae7ee9-site-associate-greenlight-fund-kansas-city-greenlight-fund-kansas-city</t>
+  </si>
+  <si>
+    <t>Site Associate, GreenLight Fund Nashville</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1a8b0034365d47eeb95f62e96ae9f6f1-site-associate-greenlight-fund-nashville-greenlight-fund-nashville</t>
+  </si>
+  <si>
+    <t>Social Media Editor, POGO Investigates</t>
+  </si>
+  <si>
+    <t>Project On Government Oversight</t>
+  </si>
+  <si>
+    <t>USD 74000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Media, Research Social Science, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3c98f16d18134bfd81de52bcba20f336-social-media-editor-pogo-investigates-project-on-government-oversight-washington</t>
+  </si>
+  <si>
+    <t>Social Video Producer and Editor</t>
+  </si>
+  <si>
+    <t>Apex for Youth</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d70533ba9b34f1abe29678949c55c3e-social-video-producer-and-editor-apex-for-youth-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Immigration Project</t>
+  </si>
+  <si>
+    <t>Volunteers of Legal Service</t>
+  </si>
+  <si>
+    <t>USD 88617.00 - 92185.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Legal Assistance, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/af99df6ce7ba4033ba59915126f3185c-staff-attorney-immigration-project-volunteers-of-legal-service-new-york</t>
+  </si>
+  <si>
+    <t>Student Support Specialist [188]</t>
+  </si>
+  <si>
+    <t>Replications, Inc</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 33.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4267541da44a47a886277122d0509a60-student-support-specialist-188-replications-inc-kings-county</t>
+  </si>
+  <si>
+    <t>Supervising Attorney: Housing Justice</t>
+  </si>
+  <si>
+    <t>TakeRoot Justice</t>
+  </si>
+  <si>
+    <t>USD 90990.00 - 104050.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/90f74885ceba4dd8a0ae898e324038c1-supervising-attorney-housing-justice-takeroot-justice-new-york</t>
+  </si>
+  <si>
+    <t>Synagogue Life Coordinator</t>
+  </si>
+  <si>
+    <t>Hinenu Baltimore</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 45000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4eba20ef6125428cae7bf3d0172f4103-synagogue-life-coordinator-hinenu-baltimore-baltimore</t>
+  </si>
+  <si>
+    <t>Vice President of Corporate Partnerships</t>
+  </si>
+  <si>
+    <t>Family Promise</t>
+  </si>
+  <si>
+    <t>USD 110000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/97150b0cd7c94833ab2796e7ad29f095-vice-president-of-corporate-partnerships-family-promise-summit</t>
+  </si>
+  <si>
+    <t>Volunteer Programs Director</t>
+  </si>
+  <si>
+    <t>OMUTUKUVU PROJECT</t>
+  </si>
+  <si>
+    <t>Mayuge, Eastern Region, UG</t>
+  </si>
+  <si>
+    <t>Children Youth, Agriculture, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8529bf4320c446a09a0a4f3f312b7e94-volunteer-programs-director-omutukuvu-project-mayuge</t>
+  </si>
+  <si>
+    <t>Children Youth, Agriculture, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/49fb35d188694227ace4696114a0442d-volunteer-programs-director-omutukuvu-project-mayuge</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1782,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1808,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2190,970 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" t="s">
+        <v>114</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F20" t="s">
+        <v>120</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" t="s">
+        <v>125</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>130</v>
+      </c>
+      <c r="F22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" t="s">
+        <v>136</v>
+      </c>
+      <c r="F23" t="s">
+        <v>137</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>139</v>
+      </c>
+      <c r="B24" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" t="s">
+        <v>142</v>
+      </c>
+      <c r="F24" t="s">
+        <v>143</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>145</v>
+      </c>
+      <c r="B25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C25" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F25" t="s">
+        <v>149</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>151</v>
+      </c>
+      <c r="B26" t="s">
+        <v>152</v>
+      </c>
+      <c r="C26" t="s">
+        <v>153</v>
+      </c>
+      <c r="D26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F26" t="s">
+        <v>131</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>156</v>
+      </c>
+      <c r="B27" t="s">
+        <v>157</v>
+      </c>
+      <c r="C27" t="s">
+        <v>158</v>
+      </c>
+      <c r="D27" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" t="s">
+        <v>159</v>
+      </c>
+      <c r="F27" t="s">
+        <v>49</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>161</v>
+      </c>
+      <c r="B28" t="s">
+        <v>162</v>
+      </c>
+      <c r="C28" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" t="s">
+        <v>164</v>
+      </c>
+      <c r="F28" t="s">
+        <v>108</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>166</v>
+      </c>
+      <c r="B29" t="s">
+        <v>167</v>
+      </c>
+      <c r="C29" t="s">
+        <v>168</v>
+      </c>
+      <c r="D29" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" t="s">
+        <v>169</v>
+      </c>
+      <c r="F29" t="s">
+        <v>131</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>171</v>
+      </c>
+      <c r="B30" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" t="s">
+        <v>173</v>
+      </c>
+      <c r="D30" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" t="s">
+        <v>174</v>
+      </c>
+      <c r="F30" t="s">
+        <v>125</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31" t="s">
+        <v>177</v>
+      </c>
+      <c r="C31" t="s">
+        <v>178</v>
+      </c>
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" t="s">
+        <v>179</v>
+      </c>
+      <c r="F31" t="s">
+        <v>125</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B32" t="s">
+        <v>182</v>
+      </c>
+      <c r="C32" t="s">
+        <v>183</v>
+      </c>
+      <c r="D32" t="s">
+        <v>90</v>
+      </c>
+      <c r="E32" t="s">
+        <v>184</v>
+      </c>
+      <c r="F32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>186</v>
+      </c>
+      <c r="B33" t="s">
+        <v>187</v>
+      </c>
+      <c r="C33" t="s">
+        <v>188</v>
+      </c>
+      <c r="D33" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" t="s">
+        <v>189</v>
+      </c>
+      <c r="F33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>191</v>
+      </c>
+      <c r="B34" t="s">
+        <v>192</v>
+      </c>
+      <c r="C34" t="s">
+        <v>193</v>
+      </c>
+      <c r="D34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" t="s">
+        <v>194</v>
+      </c>
+      <c r="F34" t="s">
+        <v>195</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>197</v>
+      </c>
+      <c r="B35" t="s">
+        <v>198</v>
+      </c>
+      <c r="C35" t="s">
+        <v>199</v>
+      </c>
+      <c r="D35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" t="s">
+        <v>200</v>
+      </c>
+      <c r="F35" t="s">
+        <v>125</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>202</v>
+      </c>
+      <c r="B36" t="s">
+        <v>167</v>
+      </c>
+      <c r="C36" t="s">
+        <v>203</v>
+      </c>
+      <c r="D36" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" t="s">
+        <v>204</v>
+      </c>
+      <c r="F36" t="s">
+        <v>205</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>207</v>
+      </c>
+      <c r="B37" t="s">
+        <v>208</v>
+      </c>
+      <c r="C37" t="s">
+        <v>209</v>
+      </c>
+      <c r="D37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" t="s">
+        <v>210</v>
+      </c>
+      <c r="F37" t="s">
+        <v>211</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>213</v>
+      </c>
+      <c r="B38" t="s">
+        <v>214</v>
+      </c>
+      <c r="C38" t="s">
+        <v>215</v>
+      </c>
+      <c r="D38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" t="s">
+        <v>91</v>
+      </c>
+      <c r="F38" t="s">
+        <v>216</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>218</v>
+      </c>
+      <c r="B39" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" t="s">
+        <v>124</v>
+      </c>
+      <c r="D39" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" t="s">
+        <v>219</v>
+      </c>
+      <c r="F39" t="s">
+        <v>49</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>221</v>
+      </c>
+      <c r="B40" t="s">
+        <v>222</v>
+      </c>
+      <c r="C40" t="s">
+        <v>223</v>
+      </c>
+      <c r="D40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" t="s">
+        <v>224</v>
+      </c>
+      <c r="F40" t="s">
+        <v>225</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>227</v>
+      </c>
+      <c r="B41" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" t="s">
+        <v>229</v>
+      </c>
+      <c r="D41" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" t="s">
+        <v>230</v>
+      </c>
+      <c r="F41" t="s">
+        <v>108</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +3209,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3248,1786 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F4" t="s">
+        <v>249</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" t="s">
+        <v>253</v>
+      </c>
+      <c r="D5" t="s">
+        <v>235</v>
+      </c>
+      <c r="E5" t="s">
+        <v>254</v>
+      </c>
+      <c r="F5" t="s">
+        <v>255</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>263</v>
+      </c>
+      <c r="B7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C7" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" t="s">
+        <v>235</v>
+      </c>
+      <c r="E7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F7" t="s">
+        <v>266</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>263</v>
+      </c>
+      <c r="B8" t="s">
+        <v>264</v>
+      </c>
+      <c r="C8" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" t="s">
+        <v>235</v>
+      </c>
+      <c r="E8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F8" t="s">
+        <v>266</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>270</v>
+      </c>
+      <c r="B9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D9" t="s">
+        <v>235</v>
+      </c>
+      <c r="E9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>270</v>
+      </c>
+      <c r="B10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C10" t="s">
+        <v>265</v>
+      </c>
+      <c r="D10" t="s">
+        <v>235</v>
+      </c>
+      <c r="E10" t="s">
+        <v>249</v>
+      </c>
+      <c r="F10" t="s">
+        <v>266</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>270</v>
+      </c>
+      <c r="B11" t="s">
+        <v>273</v>
+      </c>
+      <c r="C11" t="s">
+        <v>274</v>
+      </c>
+      <c r="D11" t="s">
+        <v>235</v>
+      </c>
+      <c r="E11" t="s">
+        <v>275</v>
+      </c>
+      <c r="F11" t="s">
+        <v>276</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>278</v>
+      </c>
+      <c r="B12" t="s">
+        <v>279</v>
+      </c>
+      <c r="C12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D12" t="s">
+        <v>235</v>
+      </c>
+      <c r="E12" t="s">
+        <v>281</v>
+      </c>
+      <c r="F12" t="s">
+        <v>282</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>284</v>
+      </c>
+      <c r="B13" t="s">
+        <v>285</v>
+      </c>
+      <c r="C13" t="s">
+        <v>234</v>
+      </c>
+      <c r="D13" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" t="s">
+        <v>286</v>
+      </c>
+      <c r="F13" t="s">
+        <v>287</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>289</v>
+      </c>
+      <c r="B14" t="s">
+        <v>290</v>
+      </c>
+      <c r="C14" t="s">
+        <v>291</v>
+      </c>
+      <c r="D14" t="s">
+        <v>235</v>
+      </c>
+      <c r="E14" t="s">
+        <v>292</v>
+      </c>
+      <c r="F14" t="s">
+        <v>293</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>295</v>
+      </c>
+      <c r="B15" t="s">
+        <v>296</v>
+      </c>
+      <c r="C15" t="s">
+        <v>297</v>
+      </c>
+      <c r="D15" t="s">
+        <v>235</v>
+      </c>
+      <c r="E15" t="s">
+        <v>298</v>
+      </c>
+      <c r="F15" t="s">
+        <v>299</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>301</v>
+      </c>
+      <c r="B16" t="s">
+        <v>302</v>
+      </c>
+      <c r="C16" t="s">
+        <v>303</v>
+      </c>
+      <c r="D16" t="s">
+        <v>242</v>
+      </c>
+      <c r="E16" t="s">
+        <v>304</v>
+      </c>
+      <c r="F16" t="s">
+        <v>305</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>307</v>
+      </c>
+      <c r="B17" t="s">
+        <v>308</v>
+      </c>
+      <c r="C17" t="s">
+        <v>309</v>
+      </c>
+      <c r="D17" t="s">
+        <v>235</v>
+      </c>
+      <c r="E17" t="s">
+        <v>310</v>
+      </c>
+      <c r="F17" t="s">
+        <v>311</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B18" t="s">
+        <v>314</v>
+      </c>
+      <c r="C18" t="s">
+        <v>315</v>
+      </c>
+      <c r="D18" t="s">
+        <v>235</v>
+      </c>
+      <c r="E18" t="s">
+        <v>316</v>
+      </c>
+      <c r="F18" t="s">
+        <v>317</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>319</v>
+      </c>
+      <c r="B19" t="s">
+        <v>320</v>
+      </c>
+      <c r="C19" t="s">
+        <v>321</v>
+      </c>
+      <c r="D19" t="s">
+        <v>235</v>
+      </c>
+      <c r="E19" t="s">
+        <v>322</v>
+      </c>
+      <c r="F19" t="s">
+        <v>323</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>325</v>
+      </c>
+      <c r="B20" t="s">
+        <v>326</v>
+      </c>
+      <c r="C20" t="s">
+        <v>268</v>
+      </c>
+      <c r="D20" t="s">
+        <v>235</v>
+      </c>
+      <c r="E20" t="s">
+        <v>327</v>
+      </c>
+      <c r="F20" t="s">
+        <v>328</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>330</v>
+      </c>
+      <c r="B21" t="s">
+        <v>331</v>
+      </c>
+      <c r="C21" t="s">
+        <v>332</v>
+      </c>
+      <c r="D21" t="s">
+        <v>235</v>
+      </c>
+      <c r="E21" t="s">
+        <v>333</v>
+      </c>
+      <c r="F21" t="s">
+        <v>334</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>336</v>
+      </c>
+      <c r="B22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C22" t="s">
+        <v>338</v>
+      </c>
+      <c r="D22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E22" t="s">
+        <v>339</v>
+      </c>
+      <c r="F22" t="s">
+        <v>249</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>341</v>
+      </c>
+      <c r="B23" t="s">
+        <v>331</v>
+      </c>
+      <c r="C23" t="s">
+        <v>332</v>
+      </c>
+      <c r="D23" t="s">
+        <v>235</v>
+      </c>
+      <c r="E23" t="s">
+        <v>342</v>
+      </c>
+      <c r="F23" t="s">
+        <v>334</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>344</v>
+      </c>
+      <c r="B24" t="s">
+        <v>345</v>
+      </c>
+      <c r="C24" t="s">
+        <v>234</v>
+      </c>
+      <c r="D24" t="s">
+        <v>235</v>
+      </c>
+      <c r="E24" t="s">
+        <v>346</v>
+      </c>
+      <c r="F24" t="s">
+        <v>347</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>349</v>
+      </c>
+      <c r="B25" t="s">
+        <v>350</v>
+      </c>
+      <c r="C25" t="s">
+        <v>291</v>
+      </c>
+      <c r="D25" t="s">
+        <v>235</v>
+      </c>
+      <c r="E25" t="s">
+        <v>351</v>
+      </c>
+      <c r="F25" t="s">
+        <v>352</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>354</v>
+      </c>
+      <c r="B26" t="s">
+        <v>355</v>
+      </c>
+      <c r="C26" t="s">
+        <v>291</v>
+      </c>
+      <c r="D26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E26" t="s">
+        <v>356</v>
+      </c>
+      <c r="F26" t="s">
+        <v>357</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>359</v>
+      </c>
+      <c r="B27" t="s">
+        <v>360</v>
+      </c>
+      <c r="C27" t="s">
+        <v>361</v>
+      </c>
+      <c r="D27" t="s">
+        <v>235</v>
+      </c>
+      <c r="E27" t="s">
+        <v>362</v>
+      </c>
+      <c r="F27" t="s">
+        <v>363</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>365</v>
+      </c>
+      <c r="B28" t="s">
+        <v>290</v>
+      </c>
+      <c r="C28" t="s">
+        <v>366</v>
+      </c>
+      <c r="D28" t="s">
+        <v>235</v>
+      </c>
+      <c r="E28" t="s">
+        <v>367</v>
+      </c>
+      <c r="F28" t="s">
+        <v>368</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>370</v>
+      </c>
+      <c r="B29" t="s">
+        <v>290</v>
+      </c>
+      <c r="C29" t="s">
+        <v>234</v>
+      </c>
+      <c r="D29" t="s">
+        <v>235</v>
+      </c>
+      <c r="E29" t="s">
+        <v>371</v>
+      </c>
+      <c r="F29" t="s">
+        <v>368</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>373</v>
+      </c>
+      <c r="B30" t="s">
+        <v>374</v>
+      </c>
+      <c r="C30" t="s">
+        <v>234</v>
+      </c>
+      <c r="D30" t="s">
+        <v>235</v>
+      </c>
+      <c r="E30" t="s">
+        <v>375</v>
+      </c>
+      <c r="F30" t="s">
+        <v>376</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>378</v>
+      </c>
+      <c r="B31" t="s">
+        <v>379</v>
+      </c>
+      <c r="C31" t="s">
+        <v>291</v>
+      </c>
+      <c r="D31" t="s">
+        <v>235</v>
+      </c>
+      <c r="E31" t="s">
+        <v>380</v>
+      </c>
+      <c r="F31" t="s">
+        <v>381</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>383</v>
+      </c>
+      <c r="B32" t="s">
+        <v>314</v>
+      </c>
+      <c r="C32" t="s">
+        <v>384</v>
+      </c>
+      <c r="D32" t="s">
+        <v>235</v>
+      </c>
+      <c r="E32" t="s">
+        <v>385</v>
+      </c>
+      <c r="F32" t="s">
+        <v>386</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>388</v>
+      </c>
+      <c r="B33" t="s">
+        <v>389</v>
+      </c>
+      <c r="C33" t="s">
+        <v>390</v>
+      </c>
+      <c r="D33" t="s">
+        <v>235</v>
+      </c>
+      <c r="E33" t="s">
+        <v>249</v>
+      </c>
+      <c r="F33" t="s">
+        <v>391</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>393</v>
+      </c>
+      <c r="B34" t="s">
+        <v>394</v>
+      </c>
+      <c r="C34" t="s">
+        <v>395</v>
+      </c>
+      <c r="D34" t="s">
+        <v>235</v>
+      </c>
+      <c r="E34" t="s">
+        <v>396</v>
+      </c>
+      <c r="F34" t="s">
+        <v>397</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>393</v>
+      </c>
+      <c r="B35" t="s">
+        <v>399</v>
+      </c>
+      <c r="C35" t="s">
+        <v>400</v>
+      </c>
+      <c r="D35" t="s">
+        <v>235</v>
+      </c>
+      <c r="E35" t="s">
+        <v>327</v>
+      </c>
+      <c r="F35" t="s">
+        <v>401</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>403</v>
+      </c>
+      <c r="B36" t="s">
+        <v>404</v>
+      </c>
+      <c r="C36" t="s">
+        <v>405</v>
+      </c>
+      <c r="D36" t="s">
+        <v>235</v>
+      </c>
+      <c r="E36" t="s">
+        <v>406</v>
+      </c>
+      <c r="F36" t="s">
+        <v>249</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>408</v>
+      </c>
+      <c r="B37" t="s">
+        <v>409</v>
+      </c>
+      <c r="C37" t="s">
+        <v>410</v>
+      </c>
+      <c r="D37" t="s">
+        <v>235</v>
+      </c>
+      <c r="E37" t="s">
+        <v>411</v>
+      </c>
+      <c r="F37" t="s">
+        <v>412</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>414</v>
+      </c>
+      <c r="B38" t="s">
+        <v>415</v>
+      </c>
+      <c r="C38" t="s">
+        <v>291</v>
+      </c>
+      <c r="D38" t="s">
+        <v>416</v>
+      </c>
+      <c r="E38" t="s">
+        <v>417</v>
+      </c>
+      <c r="F38" t="s">
+        <v>418</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>420</v>
+      </c>
+      <c r="B39" t="s">
+        <v>421</v>
+      </c>
+      <c r="C39" t="s">
+        <v>422</v>
+      </c>
+      <c r="D39" t="s">
+        <v>235</v>
+      </c>
+      <c r="E39" t="s">
+        <v>423</v>
+      </c>
+      <c r="F39" t="s">
+        <v>249</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>425</v>
+      </c>
+      <c r="B40" t="s">
+        <v>421</v>
+      </c>
+      <c r="C40" t="s">
+        <v>234</v>
+      </c>
+      <c r="D40" t="s">
+        <v>235</v>
+      </c>
+      <c r="E40" t="s">
+        <v>426</v>
+      </c>
+      <c r="F40" t="s">
+        <v>249</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>428</v>
+      </c>
+      <c r="B41" t="s">
+        <v>429</v>
+      </c>
+      <c r="C41" t="s">
+        <v>430</v>
+      </c>
+      <c r="D41" t="s">
+        <v>431</v>
+      </c>
+      <c r="E41" t="s">
+        <v>432</v>
+      </c>
+      <c r="F41" t="s">
+        <v>433</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>435</v>
+      </c>
+      <c r="B42" t="s">
+        <v>436</v>
+      </c>
+      <c r="C42" t="s">
+        <v>291</v>
+      </c>
+      <c r="D42" t="s">
+        <v>235</v>
+      </c>
+      <c r="E42" t="s">
+        <v>437</v>
+      </c>
+      <c r="F42" t="s">
+        <v>438</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>440</v>
+      </c>
+      <c r="B43" t="s">
+        <v>441</v>
+      </c>
+      <c r="C43" t="s">
+        <v>158</v>
+      </c>
+      <c r="D43" t="s">
+        <v>235</v>
+      </c>
+      <c r="E43" t="s">
+        <v>442</v>
+      </c>
+      <c r="F43" t="s">
+        <v>443</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>445</v>
+      </c>
+      <c r="B44" t="s">
+        <v>446</v>
+      </c>
+      <c r="C44" t="s">
+        <v>447</v>
+      </c>
+      <c r="D44" t="s">
+        <v>235</v>
+      </c>
+      <c r="E44" t="s">
+        <v>448</v>
+      </c>
+      <c r="F44" t="s">
+        <v>237</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>450</v>
+      </c>
+      <c r="B45" t="s">
+        <v>451</v>
+      </c>
+      <c r="C45" t="s">
+        <v>291</v>
+      </c>
+      <c r="D45" t="s">
+        <v>416</v>
+      </c>
+      <c r="E45" t="s">
+        <v>452</v>
+      </c>
+      <c r="F45" t="s">
+        <v>453</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>455</v>
+      </c>
+      <c r="B46" t="s">
+        <v>314</v>
+      </c>
+      <c r="C46" t="s">
+        <v>456</v>
+      </c>
+      <c r="D46" t="s">
+        <v>457</v>
+      </c>
+      <c r="E46" t="s">
+        <v>385</v>
+      </c>
+      <c r="F46" t="s">
+        <v>458</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>455</v>
+      </c>
+      <c r="B47" t="s">
+        <v>314</v>
+      </c>
+      <c r="C47" t="s">
+        <v>315</v>
+      </c>
+      <c r="D47" t="s">
+        <v>457</v>
+      </c>
+      <c r="E47" t="s">
+        <v>385</v>
+      </c>
+      <c r="F47" t="s">
+        <v>458</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>455</v>
+      </c>
+      <c r="B48" t="s">
+        <v>314</v>
+      </c>
+      <c r="C48" t="s">
+        <v>461</v>
+      </c>
+      <c r="D48" t="s">
+        <v>457</v>
+      </c>
+      <c r="E48" t="s">
+        <v>385</v>
+      </c>
+      <c r="F48" t="s">
+        <v>458</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>455</v>
+      </c>
+      <c r="B49" t="s">
+        <v>314</v>
+      </c>
+      <c r="C49" t="s">
+        <v>463</v>
+      </c>
+      <c r="D49" t="s">
+        <v>457</v>
+      </c>
+      <c r="E49" t="s">
+        <v>385</v>
+      </c>
+      <c r="F49" t="s">
+        <v>458</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>455</v>
+      </c>
+      <c r="B50" t="s">
+        <v>314</v>
+      </c>
+      <c r="C50" t="s">
+        <v>384</v>
+      </c>
+      <c r="D50" t="s">
+        <v>457</v>
+      </c>
+      <c r="E50" t="s">
+        <v>385</v>
+      </c>
+      <c r="F50" t="s">
+        <v>458</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>455</v>
+      </c>
+      <c r="B51" t="s">
+        <v>314</v>
+      </c>
+      <c r="C51" t="s">
+        <v>466</v>
+      </c>
+      <c r="D51" t="s">
+        <v>457</v>
+      </c>
+      <c r="E51" t="s">
+        <v>385</v>
+      </c>
+      <c r="F51" t="s">
+        <v>458</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>468</v>
+      </c>
+      <c r="B52" t="s">
+        <v>469</v>
+      </c>
+      <c r="C52" t="s">
+        <v>297</v>
+      </c>
+      <c r="D52" t="s">
+        <v>235</v>
+      </c>
+      <c r="E52" t="s">
+        <v>470</v>
+      </c>
+      <c r="F52" t="s">
+        <v>471</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>473</v>
+      </c>
+      <c r="B53" t="s">
+        <v>474</v>
+      </c>
+      <c r="C53" t="s">
+        <v>475</v>
+      </c>
+      <c r="D53" t="s">
+        <v>235</v>
+      </c>
+      <c r="E53" t="s">
+        <v>476</v>
+      </c>
+      <c r="F53" t="s">
+        <v>477</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>479</v>
+      </c>
+      <c r="B54" t="s">
+        <v>389</v>
+      </c>
+      <c r="C54" t="s">
+        <v>390</v>
+      </c>
+      <c r="D54" t="s">
+        <v>235</v>
+      </c>
+      <c r="E54" t="s">
+        <v>480</v>
+      </c>
+      <c r="F54" t="s">
+        <v>481</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>483</v>
+      </c>
+      <c r="B55" t="s">
+        <v>484</v>
+      </c>
+      <c r="C55" t="s">
+        <v>485</v>
+      </c>
+      <c r="D55" t="s">
+        <v>235</v>
+      </c>
+      <c r="E55" t="s">
+        <v>486</v>
+      </c>
+      <c r="F55" t="s">
+        <v>249</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>488</v>
+      </c>
+      <c r="B56" t="s">
+        <v>489</v>
+      </c>
+      <c r="C56" t="s">
+        <v>315</v>
+      </c>
+      <c r="D56" t="s">
+        <v>235</v>
+      </c>
+      <c r="E56" t="s">
+        <v>490</v>
+      </c>
+      <c r="F56" t="s">
+        <v>491</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>493</v>
+      </c>
+      <c r="B57" t="s">
+        <v>494</v>
+      </c>
+      <c r="C57" t="s">
+        <v>234</v>
+      </c>
+      <c r="D57" t="s">
+        <v>235</v>
+      </c>
+      <c r="E57" t="s">
+        <v>495</v>
+      </c>
+      <c r="F57" t="s">
+        <v>496</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>498</v>
+      </c>
+      <c r="B58" t="s">
+        <v>499</v>
+      </c>
+      <c r="C58" t="s">
+        <v>291</v>
+      </c>
+      <c r="D58" t="s">
+        <v>235</v>
+      </c>
+      <c r="E58" t="s">
+        <v>411</v>
+      </c>
+      <c r="F58" t="s">
+        <v>500</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>502</v>
+      </c>
+      <c r="B59" t="s">
+        <v>503</v>
+      </c>
+      <c r="C59" t="s">
+        <v>504</v>
+      </c>
+      <c r="D59" t="s">
+        <v>242</v>
+      </c>
+      <c r="E59" t="s">
+        <v>505</v>
+      </c>
+      <c r="F59" t="s">
+        <v>506</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>508</v>
+      </c>
+      <c r="B60" t="s">
+        <v>509</v>
+      </c>
+      <c r="C60" t="s">
+        <v>510</v>
+      </c>
+      <c r="D60" t="s">
+        <v>457</v>
+      </c>
+      <c r="E60" t="s">
+        <v>511</v>
+      </c>
+      <c r="F60" t="s">
+        <v>512</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>514</v>
+      </c>
+      <c r="B61" t="s">
+        <v>515</v>
+      </c>
+      <c r="C61" t="s">
+        <v>516</v>
+      </c>
+      <c r="D61" t="s">
+        <v>242</v>
+      </c>
+      <c r="E61" t="s">
+        <v>249</v>
+      </c>
+      <c r="F61" t="s">
+        <v>517</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>519</v>
+      </c>
+      <c r="B62" t="s">
+        <v>520</v>
+      </c>
+      <c r="C62" t="s">
+        <v>384</v>
+      </c>
+      <c r="D62" t="s">
+        <v>457</v>
+      </c>
+      <c r="E62" t="s">
+        <v>521</v>
+      </c>
+      <c r="F62" t="s">
+        <v>522</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>524</v>
+      </c>
+      <c r="B63" t="s">
+        <v>525</v>
+      </c>
+      <c r="C63" t="s">
+        <v>526</v>
+      </c>
+      <c r="D63" t="s">
+        <v>235</v>
+      </c>
+      <c r="E63" t="s">
+        <v>527</v>
+      </c>
+      <c r="F63" t="s">
+        <v>528</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>530</v>
+      </c>
+      <c r="B64" t="s">
+        <v>531</v>
+      </c>
+      <c r="C64" t="s">
+        <v>234</v>
+      </c>
+      <c r="D64" t="s">
+        <v>235</v>
+      </c>
+      <c r="E64" t="s">
+        <v>532</v>
+      </c>
+      <c r="F64" t="s">
+        <v>533</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>535</v>
+      </c>
+      <c r="B65" t="s">
+        <v>536</v>
+      </c>
+      <c r="C65" t="s">
+        <v>537</v>
+      </c>
+      <c r="D65" t="s">
+        <v>235</v>
+      </c>
+      <c r="E65" t="s">
+        <v>538</v>
+      </c>
+      <c r="F65" t="s">
+        <v>249</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>540</v>
+      </c>
+      <c r="B66" t="s">
+        <v>536</v>
+      </c>
+      <c r="C66" t="s">
+        <v>241</v>
+      </c>
+      <c r="D66" t="s">
+        <v>235</v>
+      </c>
+      <c r="E66" t="s">
+        <v>538</v>
+      </c>
+      <c r="F66" t="s">
+        <v>249</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>542</v>
+      </c>
+      <c r="B67" t="s">
+        <v>543</v>
+      </c>
+      <c r="C67" t="s">
+        <v>291</v>
+      </c>
+      <c r="D67" t="s">
+        <v>235</v>
+      </c>
+      <c r="E67" t="s">
+        <v>544</v>
+      </c>
+      <c r="F67" t="s">
+        <v>545</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>547</v>
+      </c>
+      <c r="B68" t="s">
+        <v>548</v>
+      </c>
+      <c r="C68" t="s">
+        <v>234</v>
+      </c>
+      <c r="D68" t="s">
+        <v>242</v>
+      </c>
+      <c r="E68" t="s">
+        <v>549</v>
+      </c>
+      <c r="F68" t="s">
+        <v>550</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>552</v>
+      </c>
+      <c r="B69" t="s">
+        <v>553</v>
+      </c>
+      <c r="C69" t="s">
+        <v>199</v>
+      </c>
+      <c r="D69" t="s">
+        <v>235</v>
+      </c>
+      <c r="E69" t="s">
+        <v>554</v>
+      </c>
+      <c r="F69" t="s">
+        <v>555</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>557</v>
+      </c>
+      <c r="B70" t="s">
+        <v>558</v>
+      </c>
+      <c r="C70" t="s">
+        <v>559</v>
+      </c>
+      <c r="D70" t="s">
+        <v>431</v>
+      </c>
+      <c r="E70" t="s">
+        <v>560</v>
+      </c>
+      <c r="F70" t="s">
+        <v>512</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>562</v>
+      </c>
+      <c r="B71" t="s">
+        <v>563</v>
+      </c>
+      <c r="C71" t="s">
+        <v>234</v>
+      </c>
+      <c r="D71" t="s">
+        <v>235</v>
+      </c>
+      <c r="E71" t="s">
+        <v>564</v>
+      </c>
+      <c r="F71" t="s">
+        <v>565</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>567</v>
+      </c>
+      <c r="B72" t="s">
+        <v>568</v>
+      </c>
+      <c r="C72" t="s">
+        <v>569</v>
+      </c>
+      <c r="D72" t="s">
+        <v>235</v>
+      </c>
+      <c r="E72" t="s">
+        <v>570</v>
+      </c>
+      <c r="F72" t="s">
+        <v>244</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>572</v>
+      </c>
+      <c r="B73" t="s">
+        <v>573</v>
+      </c>
+      <c r="C73" t="s">
+        <v>291</v>
+      </c>
+      <c r="D73" t="s">
+        <v>235</v>
+      </c>
+      <c r="E73" t="s">
+        <v>574</v>
+      </c>
+      <c r="F73" t="s">
+        <v>575</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>577</v>
+      </c>
+      <c r="B74" t="s">
+        <v>578</v>
+      </c>
+      <c r="C74" t="s">
+        <v>579</v>
+      </c>
+      <c r="D74" t="s">
+        <v>235</v>
+      </c>
+      <c r="E74" t="s">
+        <v>249</v>
+      </c>
+      <c r="F74" t="s">
+        <v>580</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>577</v>
+      </c>
+      <c r="B75" t="s">
+        <v>578</v>
+      </c>
+      <c r="C75" t="s">
+        <v>579</v>
+      </c>
+      <c r="D75" t="s">
+        <v>242</v>
+      </c>
+      <c r="E75" t="s">
+        <v>249</v>
+      </c>
+      <c r="F75" t="s">
+        <v>582</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-23.xlsx
+++ b/docs/xlsx/jobs-2026-09-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="830">
   <si>
     <t>Title</t>
   </si>
@@ -220,6 +220,24 @@
     <t>https://www.conservationjobboard.com/job-listing-environmental-review-and-permitting-specialist-batavia-new-york/7608241854</t>
   </si>
   <si>
+    <t>Environmental Social Science (Tenure Track Faculty, MES)</t>
+  </si>
+  <si>
+    <t>The Evergreen State College</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>$53,966 - $111,485 per year</t>
+  </si>
+  <si>
+    <t>policy-and-law-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-social-science-tenure-track-faculty-mes-olympia-washington/2630134276</t>
+  </si>
+  <si>
     <t>EPA Fellowship on Alternatives for Assessing Toxicity of Environmental Contaminants to Aquatic Organisms</t>
   </si>
   <si>
@@ -670,6 +688,24 @@
     <t>https://www.conservationjobboard.com/job-listing-staff-wildlife-rehabilitator-shipman-virginia/4885116627</t>
   </si>
   <si>
+    <t>Sustainable Seafood Program Assistant</t>
+  </si>
+  <si>
+    <t>SC Sea Grant Consortium</t>
+  </si>
+  <si>
+    <t>Charleston, SC</t>
+  </si>
+  <si>
+    <t>$45,000 - $55,000 per year</t>
+  </si>
+  <si>
+    <t>fisheries-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sustainable-seafood-program-assistant-charleston-south-carolina/9391336326</t>
+  </si>
+  <si>
     <t>Warehouse Associate</t>
   </si>
   <si>
@@ -754,6 +790,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/41eda023c9bf4c189a496895fb9f106a-administrative-communications-coordinator-glendale-baptist-church-nashville</t>
   </si>
   <si>
+    <t>Administrative Assistant/Paralegal</t>
+  </si>
+  <si>
+    <t>Terris, Pravlik &amp; Millian, LLP</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 57000.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/e1bac9e9b9834258ae687e4a2cb676ae-administrative-assistantparalegal-terris-pravlik-millian-llp-washington</t>
+  </si>
+  <si>
+    <t>Advocacy and Organizing Associate</t>
+  </si>
+  <si>
+    <t>The Immigrant Law Center of Minnesota</t>
+  </si>
+  <si>
+    <t>USD 75363.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fedd93a9a33d48a3ac14e9ea30d82f2a-advocacy-and-organizing-associate-the-immigrant-law-center-of-minnesota-saint-paul</t>
+  </si>
+  <si>
     <t>Assistant, Associate or Full Professor in Community Psychology</t>
   </si>
   <si>
@@ -763,9 +832,6 @@
     <t>Hewlett, New York</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/job/77b002b3c2614286a4ea790072d07f18-assistant-associate-or-full-professor-in-community-psychology-the-american-university-in-cairo-hewlett</t>
   </si>
   <si>
@@ -787,6 +853,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/a99ac586e8324e088a16bd3bac585a28-associate-director-data-hub-project-evident-boston</t>
   </si>
   <si>
+    <t>Associate Program Director, California</t>
+  </si>
+  <si>
+    <t>Conservation Lands Foundation, Inc</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 72500.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3f826f066f0b4fde9d1e0c20bf809191-associate-program-director-california-conservation-lands-foundation-inc-durango</t>
+  </si>
+  <si>
+    <t>Camp Director</t>
+  </si>
+  <si>
+    <t>Fiver Children's Foundation</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8ad9dad6a399428fa117a784d6d64519-camp-director-fiver-childrens-foundation-new-york</t>
+  </si>
+  <si>
     <t>Chief Financial and Operations Officer</t>
   </si>
   <si>
@@ -850,6 +946,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/7ad10fb5b9fe47c8848b4e1c7d68d378-chief-operating-officer-oakland-promise-oakland</t>
   </si>
   <si>
+    <t>Chief Strategy Officer</t>
+  </si>
+  <si>
+    <t>USD 220000.00 - 240000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/664311d894184277b7f0b395c1c2e6bc-chief-strategy-officer-oakland-promise-oakland</t>
+  </si>
+  <si>
     <t>Clinical Program Coordinator</t>
   </si>
   <si>
@@ -883,6 +988,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/adf9cdfe38cf430cb161871b46556451-clinician-collective-rapp-queens-day-one-ny-new-york</t>
   </si>
   <si>
+    <t>College Corner Staff (Part-Time) - Family Source Center</t>
+  </si>
+  <si>
+    <t>Jenesse Center</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 21.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Crime Safety, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/14dd6794591a4231802051006e34a40f-college-corner-staff-part-time-family-source-center-jenesse-center-los-angeles</t>
+  </si>
+  <si>
     <t>Community Development Manager</t>
   </si>
   <si>
@@ -901,6 +1024,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/87354e3c76684566972165474c60018e-community-development-manager-parkinsons-foundation-miami</t>
   </si>
   <si>
+    <t>Community Security Advisor</t>
+  </si>
+  <si>
+    <t>Jewish Federation Bay Area</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 118000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e087c28667634b02bd5b4a362f917855-community-security-advisor-jewish-federation-bay-area-san-francisco</t>
+  </si>
+  <si>
     <t>Controller</t>
   </si>
   <si>
@@ -919,6 +1060,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/787deeef13e0455d9d0a65f5426093d2-controller-food-lifeline-seattle</t>
   </si>
   <si>
+    <t>COORDINACIÓN HOSPITALARIA JALTENANGO</t>
+  </si>
+  <si>
+    <t>Compañeros En Salud</t>
+  </si>
+  <si>
+    <t>Ángel Albino Corzo, Chiapas, MX</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>MXN 26250.00 - 26250.00/month</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/582e5ec2996a448f9b4c93e7b55578ec-coordinacion-hospitalaria-jaltenango-companeros-en-salud-angel-albino-corzo</t>
+  </si>
+  <si>
     <t>Creative District Program Director</t>
   </si>
   <si>
@@ -955,6 +1117,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/cecb886a70ac493f984aa3d556c00653-cuny-office-assistant-academic-affairs-city-university-of-new-york-cuny-school-of-law-queens-county</t>
   </si>
   <si>
+    <t>Customer Success Manager</t>
+  </si>
+  <si>
+    <t>Old Friends Club</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Health Medicine, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/218866373cdb4950b5b092d7dcff2f12-customer-success-manager-old-friends-club-redmond</t>
+  </si>
+  <si>
     <t>Development Assistant</t>
   </si>
   <si>
@@ -973,6 +1153,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/f864f1b4c3d3499dadd608759d10acf9-development-assistant-the-conservation-law-foundation-boston</t>
   </si>
   <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>EcoForesters</t>
+  </si>
+  <si>
+    <t>Asheville, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Rural Areas, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b76e422b3a6b4af9b4c65fd324cea95e-development-director-ecoforesters-asheville</t>
+  </si>
+  <si>
+    <t>Development Manager (On-Site)</t>
+  </si>
+  <si>
+    <t>Young People's Chorus of NYC</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7596a136547642beb004be44ec254816-development-manager-on-site-young-peoples-chorus-of-nyc-new-york</t>
+  </si>
+  <si>
     <t>Direct Support Professional</t>
   </si>
   <si>
@@ -991,6 +1204,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/0595f1ac12524c81946cd3230d52fdfd-direct-support-professional-weachieve-inc-silver-spring</t>
   </si>
   <si>
+    <t>Director of Communications</t>
+  </si>
+  <si>
+    <t>Rennie Center for Education Research &amp; Policy</t>
+  </si>
+  <si>
+    <t>USD 99000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1dbd01dc6f7f4d8186960b48e04dc84c-director-of-communications-rennie-center-for-education-research-policy-boston</t>
+  </si>
+  <si>
     <t>Director of Community Strategy</t>
   </si>
   <si>
@@ -1048,6 +1276,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/96edf4d439e146128c315e55aaeeb850-director-of-membership-sephardic-community-center-brooklyn</t>
   </si>
   <si>
+    <t>Director of Metro Violence Prevention</t>
+  </si>
+  <si>
+    <t>Alliance for a Safe Oregon</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 82500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Crime Safety, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/788cedd5ecdc445997c00daa9915a84d-director-of-metro-violence-prevention-alliance-for-a-safe-oregon-portland</t>
+  </si>
+  <si>
+    <t>Director of Policy and Community Resilience Strategies</t>
+  </si>
+  <si>
+    <t>Race Forward</t>
+  </si>
+  <si>
+    <t>USD 98301.00 - 109053.00/year</t>
+  </si>
+  <si>
+    <t>Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ae80eb4331a54afe9d553589a1033af8-director-of-policy-and-community-resilience-strategies-race-forward-new-york</t>
+  </si>
+  <si>
     <t>Director of Technology</t>
   </si>
   <si>
@@ -1150,6 +1411,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/8bf1b9cf60ea4dd9a20d75c86c62b2d6-editorial-manager-human-rights-foundation-new-york</t>
   </si>
   <si>
+    <t>English Language Arts Teachers (Elementary School)</t>
+  </si>
+  <si>
+    <t>Tomas de Berlanga School</t>
+  </si>
+  <si>
+    <t>Puerto Ayora, (no state), EC</t>
+  </si>
+  <si>
+    <t>USD 1200.00 - 1400.00/month</t>
+  </si>
+  <si>
+    <t>Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/68e972b2aa5a4fae8b81fd98cfb175e9-english-language-arts-teachers-elementary-school-tomas-de-berlanga-school-puerto-ayora</t>
+  </si>
+  <si>
     <t>Environmental Analyst</t>
   </si>
   <si>
@@ -1225,6 +1504,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/a9d2217aa9ee48f1a3eea04c5d0d9779-executive-director-rolling-harvest-food-rescue-lumberville</t>
   </si>
   <si>
+    <t>JobsFirst</t>
+  </si>
+  <si>
+    <t>Las Vegas, Nevada</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7ee2cbd9147a4463b5d4431aa46d335d-executive-director-jobsfirst-las-vegas</t>
+  </si>
+  <si>
     <t>Facilities Manager</t>
   </si>
   <si>
@@ -1240,15 +1534,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/219bd6d1ac2d40188533c08713c84db0-facilities-manager-the-aldrich-contemporary-art-museum-ridgefield</t>
   </si>
   <si>
+    <t>Field Organizer</t>
+  </si>
+  <si>
+    <t>TSNE</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/619c982a62d54c1e83b4687535323038-field-organizer-tsne-boston</t>
+  </si>
+  <si>
     <t>Finance and Operations Manager</t>
   </si>
   <si>
     <t>Partners for a Hunger-Free Oregon</t>
   </si>
   <si>
-    <t>Portland, Oregon</t>
-  </si>
-  <si>
     <t>USD 75000.00 - 85000.00/year</t>
   </si>
   <si>
@@ -1258,15 +1561,105 @@
     <t>https://www.idealist.org/en/nonprofit-job/482ade3363f4431b803ca281ac3342c9-finance-and-operations-manager-partners-for-a-hunger-free-oregon-portland</t>
   </si>
   <si>
+    <t>Fiscal Sponsorship Coordinator</t>
+  </si>
+  <si>
+    <t>Realize Impact</t>
+  </si>
+  <si>
+    <t>Remote (CO)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 24000.00 - 38000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Climate Change, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/024e3798696c4490b18aa00f5a7fa053-fiscal-sponsorship-coordinator-realize-impact-bainbridge-island</t>
+  </si>
+  <si>
+    <t>Founding Head of Grant Development and Management—Part-Time</t>
+  </si>
+  <si>
+    <t>Urban Ag Innovations Initiatives, Inc.</t>
+  </si>
+  <si>
+    <t>USD 42.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d147b6a75af7400e894c998c03c20e3a-founding-head-of-grant-development-and-managementpart-time-urban-ag-innovations-initiatives-inc-mesa</t>
+  </si>
+  <si>
+    <t>GESTOR OPERATIVO DE SALUD COMUNITARIA</t>
+  </si>
+  <si>
+    <t>MXN 13230.00 - 13230.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d52b4a20d84a4f20b696a6a585963e1e-gestor-operativo-de-salud-comunitaria-companeros-en-salud-angel-albino-corzo</t>
+  </si>
+  <si>
+    <t>Grants Manager</t>
+  </si>
+  <si>
+    <t>Viva Farms</t>
+  </si>
+  <si>
+    <t>Mount Vernon, Washington</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 34.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80ae4dd53c9f4c61a99422fa5d2d236a-grants-manager-viva-farms-mount-vernon</t>
+  </si>
+  <si>
+    <t>Helpline Coordinator</t>
+  </si>
+  <si>
+    <t>CSSNY</t>
+  </si>
+  <si>
+    <t>USD 75196.00 - 75196.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Consumer Protection, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1865baff0e414db7a3283e39c423cb81-helpline-coordinator-cssny-new-york</t>
+  </si>
+  <si>
+    <t>Institutional Giving Manager</t>
+  </si>
+  <si>
+    <t>Mass Mentoring Partnership</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3414a45d38e145aca98c50502d46c0c1-institutional-giving-manager-mass-mentoring-partnership-boston</t>
+  </si>
+  <si>
     <t>International Director</t>
   </si>
   <si>
     <t>Swift Sports Organisation</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>USD 100.00/month</t>
   </si>
   <si>
@@ -1276,6 +1669,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/f13ff62c7fef4708abe84491b720cc93-international-director-swift-sports-organisation-kampala</t>
   </si>
   <si>
+    <t>Investment Coordinator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca3edb5f1acc4222a3c480de071e2117-investment-coordinator-realize-impact-bainbridge-island</t>
+  </si>
+  <si>
     <t>IT Support Specialist: Electronic Investigative Support Group, Rochester (6460)</t>
   </si>
   <si>
@@ -1300,6 +1699,18 @@
     <t>https://www.idealist.org/en/government-job/951aca06cb2c4ff984bcb028f8932433-it-support-specialist-medicaid-fraud-control-unit-6459-new-york-state-office-of-the-attorney-general-new-york</t>
   </si>
   <si>
+    <t>Learning Experience Coordinator</t>
+  </si>
+  <si>
+    <t>Essential Access Health</t>
+  </si>
+  <si>
+    <t>USD 65935.00 - 65935.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a148190968db47a3bb2d4e34fc119317-learning-experience-coordinator-essential-access-health-los-angeles</t>
+  </si>
+  <si>
     <t>Literacy Specialist</t>
   </si>
   <si>
@@ -1387,9 +1798,6 @@
     <t>Montpelier, Vermont</t>
   </si>
   <si>
-    <t>Full Time, Temporary</t>
-  </si>
-  <si>
     <t>Community Development, Energy, Environment</t>
   </si>
   <si>
@@ -1435,6 +1843,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/f397bbefecb645559fa1a732cdded958-office-of-developmental-disabilities-ombuds-region-2-dd-ombuds-disability-rights-washington-seattle</t>
   </si>
   <si>
+    <t>Ohio Solar Education and Outreach Coordinator (1099 Contract)</t>
+  </si>
+  <si>
+    <t>Solar United Neighbors</t>
+  </si>
+  <si>
+    <t>Cincinnati, Ohio</t>
+  </si>
+  <si>
+    <t>USD 2500.00 - 3500.00/month</t>
+  </si>
+  <si>
+    <t>Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c842919c5b543cba1163473f5dde10e-ohio-solar-education-and-outreach-coordinator-1099-contract-solar-united-neighbors-cincinnati</t>
+  </si>
+  <si>
+    <t>PA Community Canvasser: work for a better PA</t>
+  </si>
+  <si>
+    <t>UNITE HERE Local 274</t>
+  </si>
+  <si>
+    <t>Bethlehem, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 22.50 - 22.50/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/662e7892c0ba46479905f9b113f1dc97-pa-community-canvasser-work-for-a-better-pa-unite-here-local-274-bethlehem</t>
+  </si>
+  <si>
     <t>Parent to Parent Coordinator</t>
   </si>
   <si>
@@ -1453,6 +1897,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/378f1c0be41c4f1181f02d1c44eb406d-parent-to-parent-coordinator-the-arc-of-king-county-seatac</t>
   </si>
   <si>
+    <t>Persona Coordinadora de Monitoreo y Recaudación de Fondos</t>
+  </si>
+  <si>
+    <t>Peace Brigades International Colombia</t>
+  </si>
+  <si>
+    <t>Bogotá, Teusaquillo, CO</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, International Relations, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7df83388e06649b9bc08cb989c46cb7e-persona-coordinadora-de-monitoreo-y-recaudacion-de-fondos-peace-brigades-international-colombia-bogota</t>
+  </si>
+  <si>
     <t>Physical Therapist in Belize (Volunteer)</t>
   </si>
   <si>
@@ -1465,6 +1924,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/4ed05c38b3a0460f85192f27702b8101-physical-therapist-in-belize-volunteer-hillside-health-care-eldridgeville</t>
   </si>
   <si>
+    <t>Policy Associate</t>
+  </si>
+  <si>
+    <t>Central Valley Air Quality Coalition (CVAQ)</t>
+  </si>
+  <si>
+    <t>Stockton, California</t>
+  </si>
+  <si>
+    <t>USD 21.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d01d648155a4f11b123db9cbd431e44-policy-associate-central-valley-air-quality-coalition-cvaq-stockton</t>
+  </si>
+  <si>
     <t>PRIMARY STEM and Humanities positions in beach-jungle school in PUERTO RICO</t>
   </si>
   <si>
@@ -1480,6 +1957,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/ca633ba38c594095868329a3e37504fb-primary-stem-and-humanities-positions-in-beach-jungle-school-in-puerto-rico-proea-pro-educacion-y-ambiente-rincon</t>
   </si>
   <si>
+    <t>Professional Mentor/Youth Advocate</t>
+  </si>
+  <si>
+    <t>Friends of the Children-Boston</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ace5c0574407421eb0cbdd41d5d96444-professional-mentoryouth-advocate-friends-of-the-children-boston-boston</t>
+  </si>
+  <si>
     <t>Program Assistant</t>
   </si>
   <si>
@@ -1495,6 +1987,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/ffa95358ebbf4cfcb5b5f508fe5dde49-program-assistant-project-citizenship-boston</t>
   </si>
   <si>
+    <t>Program Assistant (Bilingual Spanish/English)</t>
+  </si>
+  <si>
+    <t>Operation Access (San Francisco, CA)</t>
+  </si>
+  <si>
+    <t>USD 62400.00 - 72800.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/58a964a9ac0c42d9a340678c0b3898ba-program-assistant-bilingual-spanishenglish-operation-access-san-francisco-ca-san-francisco</t>
+  </si>
+  <si>
+    <t>Program Assistant, part-time</t>
+  </si>
+  <si>
+    <t>Mark Morris Dance Group</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ead8b06e88124b128d65340fc1012441-program-assistant-part-time-mark-morris-dance-group-kings-county</t>
+  </si>
+  <si>
     <t>Program Manager - Internships</t>
   </si>
   <si>
@@ -1540,15 +2062,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/68acd7f674a641c89edff7fcdd51c940-project-assistant-collaborating-agencies-disaster-relief-effort-san-jose</t>
   </si>
   <si>
+    <t>Project Attorney, Oceans</t>
+  </si>
+  <si>
+    <t>Earthjustice</t>
+  </si>
+  <si>
+    <t>USD 116600.00 - 136000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c9f6fe572c8041cbacfa86f163df84f4-project-attorney-oceans-earthjustice-san-francisco</t>
+  </si>
+  <si>
+    <t>Project Liaison</t>
+  </si>
+  <si>
+    <t>Civilization Research Institute</t>
+  </si>
+  <si>
+    <t>Environment, Policy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/45db9b5b060242918bf32d2b526f8e00-project-liaison-civilization-research-institute-asheville</t>
+  </si>
+  <si>
     <t>Project Manager (Temporary, Full-time)</t>
   </si>
   <si>
     <t>National WIC Association</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 90000.00 - 103000.00/year</t>
   </si>
   <si>
@@ -1558,6 +2101,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/2bb112490b4d446ba6b25a03ebb3dccc-project-manager-temporary-full-time-national-wic-association-washington</t>
   </si>
   <si>
+    <t>Proposal Specialist</t>
+  </si>
+  <si>
+    <t>The Math Learning Center</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/b05d8d1dec6048dfb278098d95c9db39-proposal-specialist-the-math-learning-center-portland</t>
+  </si>
+  <si>
     <t>Psicóloga Institucional Hogar ADOLESCENTES ( es requisito viva en zona - EXCLUYENTE)</t>
   </si>
   <si>
@@ -1573,6 +2128,102 @@
     <t>https://www.idealist.org/en/nonprofit-job/d12913d8bbaa44fbb2e634e75820835a-psicologa-institucional-hogar-adolescentes-es-requisito-viva-en-zona-excluyente-hogar-de-ninos-maria-luisa-villa-ballester</t>
   </si>
   <si>
+    <t>Quality Coach</t>
+  </si>
+  <si>
+    <t>Northwest Regional Education Service District</t>
+  </si>
+  <si>
+    <t>Tillamook, Oregon</t>
+  </si>
+  <si>
+    <t>USD 29.05 - 34.71/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/a5d6b083b9cb48f99de1234a44d1578c-quality-coach-northwest-regional-education-service-district-tillamook</t>
+  </si>
+  <si>
+    <t>Rape Crisis Advocate Training Curriculum Consultant</t>
+  </si>
+  <si>
+    <t>New York City Alliance Against Sexual Assault</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>USD 81.25/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3487ab37030e4ca59d8bc97e2eb5fa30-rape-crisis-advocate-training-curriculum-consultant-new-york-city-alliance-against-sexual-assault-new-york</t>
+  </si>
+  <si>
+    <t>Regional Campaign Manager, NY &amp; NJ</t>
+  </si>
+  <si>
+    <t>Greenlight America</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37ce7bb2441541ac9106a1e4e968e21c-regional-campaign-manager-ny-nj-greenlight-america-washington</t>
+  </si>
+  <si>
+    <t>Regional Campaign Manager, Southwest</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e58f5e30d0094cd581f5c8628d2ee6c6-regional-campaign-manager-southwest-greenlight-america-washington</t>
+  </si>
+  <si>
+    <t>Research &amp; Policy Analyst, Healthy States Project</t>
+  </si>
+  <si>
+    <t>USD 102200.00 - 119400.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/eedb69b5044840cebe12d441a4c180c9-research-policy-analyst-healthy-states-project-earthjustice-washington</t>
+  </si>
+  <si>
+    <t>Resident Assistant - Senior Living Apartments</t>
+  </si>
+  <si>
+    <t>Housing Opportunities and Maintenance for the Elderly (H.O.M.E.)</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Seniors Retirement, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/54c5630018aa4cf29a70089549df1ef9-resident-assistant-senior-living-apartments-housing-opportunities-and-maintenance-for-the-elderly-home-chicago</t>
+  </si>
+  <si>
+    <t>Residential Life Education Fellow</t>
+  </si>
+  <si>
+    <t>HomeWorks Trenton</t>
+  </si>
+  <si>
+    <t>Trenton, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 37500.00 - 37500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b2975592f3624f9a95b62ae8a6aad246-residential-life-education-fellow-homeworks-trenton-trenton</t>
+  </si>
+  <si>
     <t>Resilience Corps Fellow</t>
   </si>
   <si>
@@ -1588,6 +2239,39 @@
     <t>https://www.idealist.org/en/government-job/d5fd005719df42c0b9059148f1a47a95-resilience-corps-fellow-greater-portland-council-of-governments-portland</t>
   </si>
   <si>
+    <t>Rising Wildlife Leaders - Manager</t>
+  </si>
+  <si>
+    <t>Wildlife Conservation Network</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cd2fbb07971040689e4e0a6aa2eae509-rising-wildlife-leaders-manager-wildlife-conservation-network-san-francisco</t>
+  </si>
+  <si>
+    <t>School Assistant (part-time)</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/99ed295d896d4f79abc7acbb941e1184-school-assistant-part-time-mark-morris-dance-group-kings-county</t>
+  </si>
+  <si>
+    <t>School Programs Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e9d577fb4c864fcc93e1a0d3a3024611-school-programs-manager-mark-morris-dance-group-kings-county</t>
+  </si>
+  <si>
     <t>Senior Accountant</t>
   </si>
   <si>
@@ -1606,6 +2290,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/6c1427bbbddd4fca837f0d8462f97aa9-senior-accountant-neighborhood-legal-services-program-of-the-district-of-columbia-washington</t>
   </si>
   <si>
+    <t>Senior Research &amp; Policy Analyst, Gulf Regional</t>
+  </si>
+  <si>
+    <t>Houston, Texas</t>
+  </si>
+  <si>
+    <t>USD 101200.00 - 112400.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/9adb2feb76e24dd2980a4f53d1365932-senior-research-policy-analyst-gulf-regional-earthjustice-houston</t>
+  </si>
+  <si>
     <t>Service Coordinator</t>
   </si>
   <si>
@@ -1666,9 +2362,6 @@
     <t>USD 50.00 - 50.00/hour</t>
   </si>
   <si>
-    <t>Children Youth, Civic Engagement, Community Development</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/9d70533ba9b34f1abe29678949c55c3e-social-video-producer-and-editor-apex-for-youth-new-york</t>
   </si>
   <si>
@@ -1687,15 +2380,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/af99df6ce7ba4033ba59915126f3185c-staff-attorney-immigration-project-volunteers-of-legal-service-new-york</t>
   </si>
   <si>
+    <t>Staff/Senior Attorney</t>
+  </si>
+  <si>
+    <t>Maine Equal Justice</t>
+  </si>
+  <si>
+    <t>Augusta, ME</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 82000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Poverty, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c705a6cd036f4ce680a87e58144af1ea-staffsenior-attorney-maine-equal-justice-augusta</t>
+  </si>
+  <si>
     <t>Student Support Specialist [188]</t>
   </si>
   <si>
     <t>Replications, Inc</t>
   </si>
   <si>
-    <t>Kings County, New York</t>
-  </si>
-  <si>
     <t>USD 25.00 - 33.00/hour</t>
   </si>
   <si>
@@ -1730,6 +2438,36 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/4eba20ef6125428cae7bf3d0172f4103-synagogue-life-coordinator-hinenu-baltimore-baltimore</t>
+  </si>
+  <si>
+    <t>Teaching Artist – Dance (Various Styles)</t>
+  </si>
+  <si>
+    <t>Center for Family Life in Sunset Park</t>
+  </si>
+  <si>
+    <t>USD 21.43 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2c53d82ad38c41f78f0ff4ca75d4d0b7-teaching-artist-dance-various-styles-center-for-family-life-in-sunset-park-new-york</t>
+  </si>
+  <si>
+    <t>Temporary Bilingual Test Administrator</t>
+  </si>
+  <si>
+    <t>University of Chicago Health Lab</t>
+  </si>
+  <si>
+    <t>Coachella, California</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf5c33341579428c9af09fa39ec52583-temporary-bilingual-test-administrator-university-of-chicago-health-lab-coachella</t>
   </si>
   <si>
     <t>Vice President of Corporate Partnerships</t>
@@ -2151,7 +2889,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2431,30 +3169,30 @@
         <v>70</v>
       </c>
       <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
         <v>71</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>72</v>
       </c>
-      <c r="F12" t="s">
+      <c r="H12" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s">
         <v>75</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>76</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>77</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
       </c>
       <c r="E13" t="s">
         <v>78</v>
@@ -2477,7 +3215,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
         <v>84</v>
@@ -2500,82 +3238,82 @@
         <v>89</v>
       </c>
       <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
         <v>90</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>91</v>
       </c>
-      <c r="F15" t="s">
+      <c r="H15" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" t="s">
         <v>94</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>95</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>96</v>
-      </c>
-      <c r="D16" t="s">
-        <v>25</v>
       </c>
       <c r="E16" t="s">
         <v>97</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
         <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
         <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F18" t="s">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>109</v>
@@ -2641,30 +3379,30 @@
         <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>125</v>
       </c>
       <c r="F21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D22" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s">
         <v>131</v>
@@ -2684,7 +3422,7 @@
         <v>135</v>
       </c>
       <c r="D23" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E23" t="s">
         <v>136</v>
@@ -2759,191 +3497,191 @@
         <v>154</v>
       </c>
       <c r="F26" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F27" t="s">
-        <v>49</v>
+        <v>137</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B28" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C28" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D28" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="E28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F28" t="s">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B29" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D29" t="s">
         <v>25</v>
       </c>
       <c r="E29" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F29" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B30" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C30" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D30" t="s">
         <v>25</v>
       </c>
       <c r="E30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F30" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B31" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D31" t="s">
         <v>25</v>
       </c>
       <c r="E31" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F31" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B32" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C32" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D32" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B33" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D33" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E33" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C34" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D34" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="E34" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F34" t="s">
-        <v>195</v>
+        <v>13</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>196</v>
@@ -2966,41 +3704,41 @@
         <v>200</v>
       </c>
       <c r="F35" t="s">
-        <v>125</v>
+        <v>201</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B36" t="s">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="C36" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D36" t="s">
         <v>25</v>
       </c>
       <c r="E36" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F36" t="s">
-        <v>205</v>
+        <v>131</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B37" t="s">
-        <v>208</v>
+        <v>173</v>
       </c>
       <c r="C37" t="s">
         <v>209</v>
@@ -3032,82 +3770,128 @@
         <v>25</v>
       </c>
       <c r="E38" t="s">
-        <v>91</v>
+        <v>216</v>
       </c>
       <c r="F38" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>220</v>
       </c>
       <c r="C39" t="s">
-        <v>124</v>
+        <v>221</v>
       </c>
       <c r="D39" t="s">
         <v>25</v>
       </c>
       <c r="E39" t="s">
-        <v>219</v>
+        <v>97</v>
       </c>
       <c r="F39" t="s">
-        <v>49</v>
+        <v>222</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B40" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C40" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D40" t="s">
         <v>25</v>
       </c>
       <c r="E40" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F40" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B41" t="s">
-        <v>228</v>
+        <v>129</v>
       </c>
       <c r="C41" t="s">
-        <v>229</v>
+        <v>130</v>
       </c>
       <c r="D41" t="s">
         <v>25</v>
       </c>
       <c r="E41" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F41" t="s">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>233</v>
+      </c>
+      <c r="B42" t="s">
+        <v>234</v>
+      </c>
+      <c r="C42" t="s">
+        <v>235</v>
+      </c>
+      <c r="D42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" t="s">
+        <v>236</v>
+      </c>
+      <c r="F42" t="s">
+        <v>237</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>239</v>
+      </c>
+      <c r="B43" t="s">
+        <v>240</v>
+      </c>
+      <c r="C43" t="s">
+        <v>241</v>
+      </c>
+      <c r="D43" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" t="s">
+        <v>242</v>
+      </c>
+      <c r="F43" t="s">
+        <v>114</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -3153,6 +3937,8 @@
     <hyperlink ref="H39" r:id="rId38"/>
     <hyperlink ref="H40" r:id="rId39"/>
     <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3209,7 +3995,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3250,1704 +4036,2831 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="B2" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C2" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D2" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E2" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="F2" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C3" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D3" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E3" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="F3" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B4" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E4" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="F4" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="B5" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C5" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="D5" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E5" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="F5" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B6" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C6" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="D6" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B7" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C7" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D7" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E7" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="F7" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B8" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="C8" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="D8" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E8" t="s">
-        <v>249</v>
+        <v>282</v>
       </c>
       <c r="F8" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="B9" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="C9" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="D9" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F9" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="B10" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="C10" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="D10" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E10" t="s">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="F10" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="B11" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="C11" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="D11" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E11" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="F11" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="B12" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="C12" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="D12" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E12" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="F12" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="B13" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="C13" t="s">
-        <v>234</v>
+        <v>300</v>
       </c>
       <c r="D13" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E13" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="F13" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="B14" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C14" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D14" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E14" t="s">
-        <v>292</v>
+        <v>262</v>
       </c>
       <c r="F14" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B15" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C15" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="D15" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E15" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="F15" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B16" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C16" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D16" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E16" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="F16" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B17" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C17" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="D17" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E17" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F17" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B18" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C18" t="s">
-        <v>315</v>
+        <v>246</v>
       </c>
       <c r="D18" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E18" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F18" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B19" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C19" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D19" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="E19" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="F19" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B20" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C20" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="D20" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E20" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F20" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B21" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C21" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="D21" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E21" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F21" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B22" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C22" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D22" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E22" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="F22" t="s">
-        <v>249</v>
+        <v>346</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B23" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="C23" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="D23" t="s">
-        <v>235</v>
+        <v>351</v>
       </c>
       <c r="E23" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="F23" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="B24" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="C24" t="s">
-        <v>234</v>
+        <v>357</v>
       </c>
       <c r="D24" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="E24" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="F24" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="B25" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="C25" t="s">
-        <v>291</v>
+        <v>363</v>
       </c>
       <c r="D25" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E25" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="F25" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="B26" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="C26" t="s">
-        <v>291</v>
+        <v>369</v>
       </c>
       <c r="D26" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E26" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="F26" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B27" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="C27" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="D27" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E27" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="F27" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B28" t="s">
-        <v>290</v>
+        <v>380</v>
       </c>
       <c r="C28" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="D28" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E28" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="F28" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="B29" t="s">
-        <v>290</v>
+        <v>386</v>
       </c>
       <c r="C29" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D29" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E29" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="F29" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="B30" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="C30" t="s">
-        <v>234</v>
+        <v>392</v>
       </c>
       <c r="D30" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E30" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="F30" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="B31" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C31" t="s">
-        <v>291</v>
+        <v>375</v>
       </c>
       <c r="D31" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E31" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="F31" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="B32" t="s">
-        <v>314</v>
+        <v>402</v>
       </c>
       <c r="C32" t="s">
-        <v>384</v>
+        <v>300</v>
       </c>
       <c r="D32" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E32" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="F32" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="B33" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C33" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="D33" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E33" t="s">
-        <v>249</v>
+        <v>409</v>
       </c>
       <c r="F33" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="B34" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="C34" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="D34" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E34" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="F34" t="s">
-        <v>397</v>
+        <v>262</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="B35" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C35" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="D35" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E35" t="s">
-        <v>327</v>
+        <v>418</v>
       </c>
       <c r="F35" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>402</v>
+        <v>419</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="B36" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="C36" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="D36" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E36" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="F36" t="s">
-        <v>249</v>
+        <v>424</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="B37" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="C37" t="s">
-        <v>410</v>
+        <v>281</v>
       </c>
       <c r="D37" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E37" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="F37" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="B38" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="C38" t="s">
-        <v>291</v>
+        <v>246</v>
       </c>
       <c r="D38" t="s">
-        <v>416</v>
+        <v>247</v>
       </c>
       <c r="E38" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="F38" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="B39" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="C39" t="s">
-        <v>422</v>
+        <v>332</v>
       </c>
       <c r="D39" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E39" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="F39" t="s">
-        <v>249</v>
+        <v>439</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="B40" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="C40" t="s">
-        <v>234</v>
+        <v>332</v>
       </c>
       <c r="D40" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E40" t="s">
-        <v>426</v>
+        <v>443</v>
       </c>
       <c r="F40" t="s">
-        <v>249</v>
+        <v>444</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="B41" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="C41" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="D41" t="s">
-        <v>431</v>
+        <v>247</v>
       </c>
       <c r="E41" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="F41" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="B42" t="s">
-        <v>436</v>
+        <v>331</v>
       </c>
       <c r="C42" t="s">
-        <v>291</v>
+        <v>453</v>
       </c>
       <c r="D42" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E42" t="s">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="F42" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="B43" t="s">
-        <v>441</v>
+        <v>331</v>
       </c>
       <c r="C43" t="s">
-        <v>158</v>
+        <v>246</v>
       </c>
       <c r="D43" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E43" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="F43" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="B44" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="C44" t="s">
-        <v>447</v>
+        <v>246</v>
       </c>
       <c r="D44" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E44" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="F44" t="s">
-        <v>237</v>
+        <v>463</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="B45" t="s">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="C45" t="s">
-        <v>291</v>
+        <v>467</v>
       </c>
       <c r="D45" t="s">
-        <v>416</v>
+        <v>247</v>
       </c>
       <c r="E45" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="F45" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="B46" t="s">
-        <v>314</v>
+        <v>472</v>
       </c>
       <c r="C46" t="s">
-        <v>456</v>
+        <v>332</v>
       </c>
       <c r="D46" t="s">
-        <v>457</v>
+        <v>247</v>
       </c>
       <c r="E46" t="s">
-        <v>385</v>
+        <v>473</v>
       </c>
       <c r="F46" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="B47" t="s">
-        <v>314</v>
+        <v>374</v>
       </c>
       <c r="C47" t="s">
-        <v>315</v>
+        <v>477</v>
       </c>
       <c r="D47" t="s">
-        <v>457</v>
+        <v>247</v>
       </c>
       <c r="E47" t="s">
-        <v>385</v>
+        <v>478</v>
       </c>
       <c r="F47" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="B48" t="s">
-        <v>314</v>
+        <v>482</v>
       </c>
       <c r="C48" t="s">
-        <v>461</v>
+        <v>483</v>
       </c>
       <c r="D48" t="s">
-        <v>457</v>
+        <v>247</v>
       </c>
       <c r="E48" t="s">
-        <v>385</v>
+        <v>262</v>
       </c>
       <c r="F48" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="B49" t="s">
-        <v>314</v>
+        <v>487</v>
       </c>
       <c r="C49" t="s">
-        <v>463</v>
+        <v>488</v>
       </c>
       <c r="D49" t="s">
-        <v>457</v>
+        <v>247</v>
       </c>
       <c r="E49" t="s">
-        <v>385</v>
+        <v>489</v>
       </c>
       <c r="F49" t="s">
-        <v>458</v>
+        <v>490</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>464</v>
+        <v>491</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="B50" t="s">
-        <v>314</v>
+        <v>492</v>
       </c>
       <c r="C50" t="s">
-        <v>384</v>
+        <v>493</v>
       </c>
       <c r="D50" t="s">
-        <v>457</v>
+        <v>247</v>
       </c>
       <c r="E50" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="F50" t="s">
-        <v>458</v>
+        <v>494</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>465</v>
+        <v>495</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="B51" t="s">
-        <v>314</v>
+        <v>496</v>
       </c>
       <c r="C51" t="s">
-        <v>466</v>
+        <v>497</v>
       </c>
       <c r="D51" t="s">
-        <v>457</v>
+        <v>247</v>
       </c>
       <c r="E51" t="s">
-        <v>385</v>
+        <v>498</v>
       </c>
       <c r="F51" t="s">
-        <v>458</v>
+        <v>499</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>467</v>
+        <v>500</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>468</v>
+        <v>501</v>
       </c>
       <c r="B52" t="s">
-        <v>469</v>
+        <v>502</v>
       </c>
       <c r="C52" t="s">
-        <v>297</v>
+        <v>503</v>
       </c>
       <c r="D52" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E52" t="s">
-        <v>470</v>
+        <v>504</v>
       </c>
       <c r="F52" t="s">
-        <v>471</v>
+        <v>262</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>472</v>
+        <v>505</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>473</v>
+        <v>506</v>
       </c>
       <c r="B53" t="s">
-        <v>474</v>
+        <v>507</v>
       </c>
       <c r="C53" t="s">
-        <v>475</v>
+        <v>375</v>
       </c>
       <c r="D53" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E53" t="s">
-        <v>476</v>
+        <v>508</v>
       </c>
       <c r="F53" t="s">
-        <v>477</v>
+        <v>262</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>478</v>
+        <v>509</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>479</v>
+        <v>510</v>
       </c>
       <c r="B54" t="s">
-        <v>389</v>
+        <v>511</v>
       </c>
       <c r="C54" t="s">
-        <v>390</v>
+        <v>422</v>
       </c>
       <c r="D54" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E54" t="s">
-        <v>480</v>
+        <v>512</v>
       </c>
       <c r="F54" t="s">
-        <v>481</v>
+        <v>513</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>482</v>
+        <v>514</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>483</v>
+        <v>515</v>
       </c>
       <c r="B55" t="s">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="C55" t="s">
-        <v>485</v>
+        <v>517</v>
       </c>
       <c r="D55" t="s">
-        <v>235</v>
+        <v>518</v>
       </c>
       <c r="E55" t="s">
-        <v>486</v>
+        <v>519</v>
       </c>
       <c r="F55" t="s">
-        <v>249</v>
+        <v>520</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>487</v>
+        <v>521</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>488</v>
+        <v>522</v>
       </c>
       <c r="B56" t="s">
-        <v>489</v>
+        <v>523</v>
       </c>
       <c r="C56" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="D56" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="E56" t="s">
-        <v>490</v>
+        <v>524</v>
       </c>
       <c r="F56" t="s">
-        <v>491</v>
+        <v>525</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>492</v>
+        <v>526</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>493</v>
+        <v>527</v>
       </c>
       <c r="B57" t="s">
-        <v>494</v>
+        <v>349</v>
       </c>
       <c r="C57" t="s">
-        <v>234</v>
+        <v>350</v>
       </c>
       <c r="D57" t="s">
-        <v>235</v>
+        <v>351</v>
       </c>
       <c r="E57" t="s">
-        <v>495</v>
+        <v>528</v>
       </c>
       <c r="F57" t="s">
-        <v>496</v>
+        <v>353</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>497</v>
+        <v>529</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>498</v>
+        <v>530</v>
       </c>
       <c r="B58" t="s">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="C58" t="s">
-        <v>291</v>
+        <v>532</v>
       </c>
       <c r="D58" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E58" t="s">
-        <v>411</v>
+        <v>533</v>
       </c>
       <c r="F58" t="s">
-        <v>500</v>
+        <v>534</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>501</v>
+        <v>535</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>502</v>
+        <v>536</v>
       </c>
       <c r="B59" t="s">
-        <v>503</v>
+        <v>537</v>
       </c>
       <c r="C59" t="s">
-        <v>504</v>
+        <v>246</v>
       </c>
       <c r="D59" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E59" t="s">
-        <v>505</v>
+        <v>538</v>
       </c>
       <c r="F59" t="s">
-        <v>506</v>
+        <v>539</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>507</v>
+        <v>540</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>508</v>
+        <v>541</v>
       </c>
       <c r="B60" t="s">
-        <v>509</v>
+        <v>542</v>
       </c>
       <c r="C60" t="s">
-        <v>510</v>
+        <v>375</v>
       </c>
       <c r="D60" t="s">
-        <v>457</v>
+        <v>247</v>
       </c>
       <c r="E60" t="s">
-        <v>511</v>
+        <v>543</v>
       </c>
       <c r="F60" t="s">
-        <v>512</v>
+        <v>544</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>513</v>
+        <v>545</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>514</v>
+        <v>546</v>
       </c>
       <c r="B61" t="s">
-        <v>515</v>
+        <v>547</v>
       </c>
       <c r="C61" t="s">
-        <v>516</v>
+        <v>332</v>
       </c>
       <c r="D61" t="s">
-        <v>242</v>
+        <v>518</v>
       </c>
       <c r="E61" t="s">
-        <v>249</v>
+        <v>548</v>
       </c>
       <c r="F61" t="s">
-        <v>517</v>
+        <v>549</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>551</v>
+      </c>
+      <c r="B62" t="s">
+        <v>516</v>
+      </c>
+      <c r="C62" t="s">
+        <v>517</v>
+      </c>
+      <c r="D62" t="s">
+        <v>518</v>
+      </c>
+      <c r="E62" t="s">
         <v>519</v>
       </c>
-      <c r="B62" t="s">
+      <c r="F62" t="s">
         <v>520</v>
       </c>
-      <c r="C62" t="s">
-        <v>384</v>
-      </c>
-      <c r="D62" t="s">
-        <v>457</v>
-      </c>
-      <c r="E62" t="s">
-        <v>521</v>
-      </c>
-      <c r="F62" t="s">
-        <v>522</v>
-      </c>
       <c r="H62" s="2" t="s">
-        <v>523</v>
+        <v>552</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>524</v>
+        <v>553</v>
       </c>
       <c r="B63" t="s">
-        <v>525</v>
+        <v>554</v>
       </c>
       <c r="C63" t="s">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="D63" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E63" t="s">
-        <v>527</v>
+        <v>556</v>
       </c>
       <c r="F63" t="s">
-        <v>528</v>
+        <v>262</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>529</v>
+        <v>557</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>530</v>
+        <v>558</v>
       </c>
       <c r="B64" t="s">
-        <v>531</v>
+        <v>554</v>
       </c>
       <c r="C64" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D64" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E64" t="s">
-        <v>532</v>
+        <v>559</v>
       </c>
       <c r="F64" t="s">
-        <v>533</v>
+        <v>262</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>535</v>
+        <v>561</v>
       </c>
       <c r="B65" t="s">
-        <v>536</v>
+        <v>562</v>
       </c>
       <c r="C65" t="s">
-        <v>537</v>
+        <v>326</v>
       </c>
       <c r="D65" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E65" t="s">
-        <v>538</v>
+        <v>563</v>
       </c>
       <c r="F65" t="s">
-        <v>249</v>
+        <v>455</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>539</v>
+        <v>564</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>540</v>
+        <v>565</v>
       </c>
       <c r="B66" t="s">
-        <v>536</v>
+        <v>566</v>
       </c>
       <c r="C66" t="s">
-        <v>241</v>
+        <v>567</v>
       </c>
       <c r="D66" t="s">
-        <v>235</v>
+        <v>568</v>
       </c>
       <c r="E66" t="s">
-        <v>538</v>
+        <v>569</v>
       </c>
       <c r="F66" t="s">
-        <v>249</v>
+        <v>570</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>541</v>
+        <v>571</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>542</v>
+        <v>572</v>
       </c>
       <c r="B67" t="s">
-        <v>543</v>
+        <v>573</v>
       </c>
       <c r="C67" t="s">
-        <v>291</v>
+        <v>332</v>
       </c>
       <c r="D67" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E67" t="s">
-        <v>544</v>
+        <v>574</v>
       </c>
       <c r="F67" t="s">
-        <v>545</v>
+        <v>575</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>546</v>
+        <v>576</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>547</v>
+        <v>577</v>
       </c>
       <c r="B68" t="s">
-        <v>548</v>
+        <v>578</v>
       </c>
       <c r="C68" t="s">
-        <v>234</v>
+        <v>164</v>
       </c>
       <c r="D68" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E68" t="s">
-        <v>549</v>
+        <v>579</v>
       </c>
       <c r="F68" t="s">
-        <v>550</v>
+        <v>580</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>552</v>
+        <v>582</v>
       </c>
       <c r="B69" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
       <c r="C69" t="s">
-        <v>199</v>
+        <v>584</v>
       </c>
       <c r="D69" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E69" t="s">
-        <v>554</v>
+        <v>585</v>
       </c>
       <c r="F69" t="s">
-        <v>555</v>
+        <v>249</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>556</v>
+        <v>586</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>557</v>
+        <v>587</v>
       </c>
       <c r="B70" t="s">
-        <v>558</v>
+        <v>588</v>
       </c>
       <c r="C70" t="s">
-        <v>559</v>
+        <v>332</v>
       </c>
       <c r="D70" t="s">
-        <v>431</v>
+        <v>518</v>
       </c>
       <c r="E70" t="s">
-        <v>560</v>
+        <v>589</v>
       </c>
       <c r="F70" t="s">
-        <v>512</v>
+        <v>590</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>561</v>
+        <v>591</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="B71" t="s">
-        <v>563</v>
+        <v>374</v>
       </c>
       <c r="C71" t="s">
-        <v>234</v>
+        <v>593</v>
       </c>
       <c r="D71" t="s">
-        <v>235</v>
+        <v>351</v>
       </c>
       <c r="E71" t="s">
-        <v>564</v>
+        <v>478</v>
       </c>
       <c r="F71" t="s">
-        <v>565</v>
+        <v>594</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>566</v>
+        <v>595</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>567</v>
+        <v>592</v>
       </c>
       <c r="B72" t="s">
-        <v>568</v>
+        <v>374</v>
       </c>
       <c r="C72" t="s">
-        <v>569</v>
+        <v>375</v>
       </c>
       <c r="D72" t="s">
-        <v>235</v>
+        <v>351</v>
       </c>
       <c r="E72" t="s">
-        <v>570</v>
+        <v>478</v>
       </c>
       <c r="F72" t="s">
-        <v>244</v>
+        <v>594</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>571</v>
+        <v>596</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>572</v>
+        <v>592</v>
       </c>
       <c r="B73" t="s">
-        <v>573</v>
+        <v>374</v>
       </c>
       <c r="C73" t="s">
-        <v>291</v>
+        <v>597</v>
       </c>
       <c r="D73" t="s">
-        <v>235</v>
+        <v>351</v>
       </c>
       <c r="E73" t="s">
-        <v>574</v>
+        <v>478</v>
       </c>
       <c r="F73" t="s">
-        <v>575</v>
+        <v>594</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>576</v>
+        <v>598</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>577</v>
+        <v>592</v>
       </c>
       <c r="B74" t="s">
-        <v>578</v>
+        <v>374</v>
       </c>
       <c r="C74" t="s">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="D74" t="s">
-        <v>235</v>
+        <v>351</v>
       </c>
       <c r="E74" t="s">
-        <v>249</v>
+        <v>478</v>
       </c>
       <c r="F74" t="s">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>581</v>
+        <v>600</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>577</v>
+        <v>592</v>
       </c>
       <c r="B75" t="s">
-        <v>578</v>
+        <v>374</v>
       </c>
       <c r="C75" t="s">
-        <v>579</v>
+        <v>477</v>
       </c>
       <c r="D75" t="s">
-        <v>242</v>
+        <v>351</v>
       </c>
       <c r="E75" t="s">
-        <v>249</v>
+        <v>478</v>
       </c>
       <c r="F75" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>583</v>
+        <v>601</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>592</v>
+      </c>
+      <c r="B76" t="s">
+        <v>374</v>
+      </c>
+      <c r="C76" t="s">
+        <v>602</v>
+      </c>
+      <c r="D76" t="s">
+        <v>351</v>
+      </c>
+      <c r="E76" t="s">
+        <v>478</v>
+      </c>
+      <c r="F76" t="s">
+        <v>594</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>604</v>
+      </c>
+      <c r="B77" t="s">
+        <v>605</v>
+      </c>
+      <c r="C77" t="s">
+        <v>344</v>
+      </c>
+      <c r="D77" t="s">
+        <v>247</v>
+      </c>
+      <c r="E77" t="s">
+        <v>606</v>
+      </c>
+      <c r="F77" t="s">
+        <v>607</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>609</v>
+      </c>
+      <c r="B78" t="s">
+        <v>610</v>
+      </c>
+      <c r="C78" t="s">
+        <v>611</v>
+      </c>
+      <c r="D78" t="s">
+        <v>518</v>
+      </c>
+      <c r="E78" t="s">
+        <v>612</v>
+      </c>
+      <c r="F78" t="s">
+        <v>613</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>615</v>
+      </c>
+      <c r="B79" t="s">
+        <v>616</v>
+      </c>
+      <c r="C79" t="s">
+        <v>617</v>
+      </c>
+      <c r="D79" t="s">
+        <v>351</v>
+      </c>
+      <c r="E79" t="s">
+        <v>618</v>
+      </c>
+      <c r="F79" t="s">
+        <v>619</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>621</v>
+      </c>
+      <c r="B80" t="s">
+        <v>622</v>
+      </c>
+      <c r="C80" t="s">
+        <v>623</v>
+      </c>
+      <c r="D80" t="s">
+        <v>247</v>
+      </c>
+      <c r="E80" t="s">
+        <v>624</v>
+      </c>
+      <c r="F80" t="s">
+        <v>625</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>627</v>
+      </c>
+      <c r="B81" t="s">
+        <v>628</v>
+      </c>
+      <c r="C81" t="s">
+        <v>629</v>
+      </c>
+      <c r="D81" t="s">
+        <v>247</v>
+      </c>
+      <c r="E81" t="s">
+        <v>262</v>
+      </c>
+      <c r="F81" t="s">
+        <v>630</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>632</v>
+      </c>
+      <c r="B82" t="s">
+        <v>482</v>
+      </c>
+      <c r="C82" t="s">
+        <v>483</v>
+      </c>
+      <c r="D82" t="s">
+        <v>247</v>
+      </c>
+      <c r="E82" t="s">
+        <v>633</v>
+      </c>
+      <c r="F82" t="s">
+        <v>634</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>636</v>
+      </c>
+      <c r="B83" t="s">
+        <v>637</v>
+      </c>
+      <c r="C83" t="s">
+        <v>638</v>
+      </c>
+      <c r="D83" t="s">
+        <v>568</v>
+      </c>
+      <c r="E83" t="s">
+        <v>639</v>
+      </c>
+      <c r="F83" t="s">
+        <v>640</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>642</v>
+      </c>
+      <c r="B84" t="s">
+        <v>643</v>
+      </c>
+      <c r="C84" t="s">
+        <v>644</v>
+      </c>
+      <c r="D84" t="s">
+        <v>247</v>
+      </c>
+      <c r="E84" t="s">
+        <v>645</v>
+      </c>
+      <c r="F84" t="s">
+        <v>262</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>647</v>
+      </c>
+      <c r="B85" t="s">
+        <v>648</v>
+      </c>
+      <c r="C85" t="s">
+        <v>375</v>
+      </c>
+      <c r="D85" t="s">
+        <v>247</v>
+      </c>
+      <c r="E85" t="s">
+        <v>649</v>
+      </c>
+      <c r="F85" t="s">
+        <v>650</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>652</v>
+      </c>
+      <c r="B86" t="s">
+        <v>653</v>
+      </c>
+      <c r="C86" t="s">
+        <v>375</v>
+      </c>
+      <c r="D86" t="s">
+        <v>247</v>
+      </c>
+      <c r="E86" t="s">
+        <v>654</v>
+      </c>
+      <c r="F86" t="s">
+        <v>655</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>657</v>
+      </c>
+      <c r="B87" t="s">
+        <v>658</v>
+      </c>
+      <c r="C87" t="s">
+        <v>338</v>
+      </c>
+      <c r="D87" t="s">
+        <v>247</v>
+      </c>
+      <c r="E87" t="s">
+        <v>659</v>
+      </c>
+      <c r="F87" t="s">
+        <v>660</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>662</v>
+      </c>
+      <c r="B88" t="s">
+        <v>663</v>
+      </c>
+      <c r="C88" t="s">
+        <v>664</v>
+      </c>
+      <c r="D88" t="s">
+        <v>254</v>
+      </c>
+      <c r="E88" t="s">
+        <v>665</v>
+      </c>
+      <c r="F88" t="s">
+        <v>262</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>667</v>
+      </c>
+      <c r="B89" t="s">
+        <v>668</v>
+      </c>
+      <c r="C89" t="s">
+        <v>246</v>
+      </c>
+      <c r="D89" t="s">
+        <v>247</v>
+      </c>
+      <c r="E89" t="s">
+        <v>669</v>
+      </c>
+      <c r="F89" t="s">
+        <v>670</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>672</v>
+      </c>
+      <c r="B90" t="s">
+        <v>673</v>
+      </c>
+      <c r="C90" t="s">
+        <v>332</v>
+      </c>
+      <c r="D90" t="s">
+        <v>247</v>
+      </c>
+      <c r="E90" t="s">
+        <v>512</v>
+      </c>
+      <c r="F90" t="s">
+        <v>674</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>676</v>
+      </c>
+      <c r="B91" t="s">
+        <v>677</v>
+      </c>
+      <c r="C91" t="s">
+        <v>678</v>
+      </c>
+      <c r="D91" t="s">
+        <v>254</v>
+      </c>
+      <c r="E91" t="s">
+        <v>679</v>
+      </c>
+      <c r="F91" t="s">
+        <v>680</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>682</v>
+      </c>
+      <c r="B92" t="s">
+        <v>683</v>
+      </c>
+      <c r="C92" t="s">
+        <v>338</v>
+      </c>
+      <c r="D92" t="s">
+        <v>247</v>
+      </c>
+      <c r="E92" t="s">
+        <v>684</v>
+      </c>
+      <c r="F92" t="s">
+        <v>262</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>686</v>
+      </c>
+      <c r="B93" t="s">
+        <v>687</v>
+      </c>
+      <c r="C93" t="s">
+        <v>381</v>
+      </c>
+      <c r="D93" t="s">
+        <v>247</v>
+      </c>
+      <c r="E93" t="s">
+        <v>262</v>
+      </c>
+      <c r="F93" t="s">
+        <v>688</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>690</v>
+      </c>
+      <c r="B94" t="s">
+        <v>691</v>
+      </c>
+      <c r="C94" t="s">
+        <v>260</v>
+      </c>
+      <c r="D94" t="s">
+        <v>351</v>
+      </c>
+      <c r="E94" t="s">
+        <v>692</v>
+      </c>
+      <c r="F94" t="s">
+        <v>693</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>695</v>
+      </c>
+      <c r="B95" t="s">
+        <v>696</v>
+      </c>
+      <c r="C95" t="s">
+        <v>697</v>
+      </c>
+      <c r="D95" t="s">
+        <v>247</v>
+      </c>
+      <c r="E95" t="s">
+        <v>262</v>
+      </c>
+      <c r="F95" t="s">
+        <v>262</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>699</v>
+      </c>
+      <c r="B96" t="s">
+        <v>700</v>
+      </c>
+      <c r="C96" t="s">
+        <v>701</v>
+      </c>
+      <c r="D96" t="s">
+        <v>254</v>
+      </c>
+      <c r="E96" t="s">
+        <v>262</v>
+      </c>
+      <c r="F96" t="s">
+        <v>702</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>704</v>
+      </c>
+      <c r="B97" t="s">
+        <v>705</v>
+      </c>
+      <c r="C97" t="s">
+        <v>706</v>
+      </c>
+      <c r="D97" t="s">
+        <v>247</v>
+      </c>
+      <c r="E97" t="s">
+        <v>707</v>
+      </c>
+      <c r="F97" t="s">
+        <v>708</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>710</v>
+      </c>
+      <c r="B98" t="s">
+        <v>711</v>
+      </c>
+      <c r="C98" t="s">
+        <v>712</v>
+      </c>
+      <c r="D98" t="s">
+        <v>518</v>
+      </c>
+      <c r="E98" t="s">
+        <v>713</v>
+      </c>
+      <c r="F98" t="s">
+        <v>714</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>716</v>
+      </c>
+      <c r="B99" t="s">
+        <v>717</v>
+      </c>
+      <c r="C99" t="s">
+        <v>332</v>
+      </c>
+      <c r="D99" t="s">
+        <v>247</v>
+      </c>
+      <c r="E99" t="s">
+        <v>473</v>
+      </c>
+      <c r="F99" t="s">
+        <v>718</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>720</v>
+      </c>
+      <c r="B100" t="s">
+        <v>717</v>
+      </c>
+      <c r="C100" t="s">
+        <v>332</v>
+      </c>
+      <c r="D100" t="s">
+        <v>247</v>
+      </c>
+      <c r="E100" t="s">
+        <v>473</v>
+      </c>
+      <c r="F100" t="s">
+        <v>718</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>722</v>
+      </c>
+      <c r="B101" t="s">
+        <v>683</v>
+      </c>
+      <c r="C101" t="s">
+        <v>260</v>
+      </c>
+      <c r="D101" t="s">
+        <v>247</v>
+      </c>
+      <c r="E101" t="s">
+        <v>723</v>
+      </c>
+      <c r="F101" t="s">
+        <v>262</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>725</v>
+      </c>
+      <c r="B102" t="s">
+        <v>726</v>
+      </c>
+      <c r="C102" t="s">
+        <v>727</v>
+      </c>
+      <c r="D102" t="s">
+        <v>518</v>
+      </c>
+      <c r="E102" t="s">
+        <v>262</v>
+      </c>
+      <c r="F102" t="s">
+        <v>728</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>730</v>
+      </c>
+      <c r="B103" t="s">
+        <v>731</v>
+      </c>
+      <c r="C103" t="s">
+        <v>732</v>
+      </c>
+      <c r="D103" t="s">
+        <v>351</v>
+      </c>
+      <c r="E103" t="s">
+        <v>733</v>
+      </c>
+      <c r="F103" t="s">
+        <v>734</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>736</v>
+      </c>
+      <c r="B104" t="s">
+        <v>737</v>
+      </c>
+      <c r="C104" t="s">
+        <v>477</v>
+      </c>
+      <c r="D104" t="s">
+        <v>351</v>
+      </c>
+      <c r="E104" t="s">
+        <v>738</v>
+      </c>
+      <c r="F104" t="s">
+        <v>739</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>741</v>
+      </c>
+      <c r="B105" t="s">
+        <v>742</v>
+      </c>
+      <c r="C105" t="s">
+        <v>332</v>
+      </c>
+      <c r="D105" t="s">
+        <v>247</v>
+      </c>
+      <c r="E105" t="s">
+        <v>743</v>
+      </c>
+      <c r="F105" t="s">
+        <v>744</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>746</v>
+      </c>
+      <c r="B106" t="s">
+        <v>663</v>
+      </c>
+      <c r="C106" t="s">
+        <v>664</v>
+      </c>
+      <c r="D106" t="s">
+        <v>254</v>
+      </c>
+      <c r="E106" t="s">
+        <v>747</v>
+      </c>
+      <c r="F106" t="s">
+        <v>748</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>750</v>
+      </c>
+      <c r="B107" t="s">
+        <v>663</v>
+      </c>
+      <c r="C107" t="s">
+        <v>664</v>
+      </c>
+      <c r="D107" t="s">
+        <v>247</v>
+      </c>
+      <c r="E107" t="s">
+        <v>370</v>
+      </c>
+      <c r="F107" t="s">
+        <v>748</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>752</v>
+      </c>
+      <c r="B108" t="s">
+        <v>753</v>
+      </c>
+      <c r="C108" t="s">
+        <v>754</v>
+      </c>
+      <c r="D108" t="s">
+        <v>247</v>
+      </c>
+      <c r="E108" t="s">
+        <v>755</v>
+      </c>
+      <c r="F108" t="s">
+        <v>756</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>758</v>
+      </c>
+      <c r="B109" t="s">
+        <v>683</v>
+      </c>
+      <c r="C109" t="s">
+        <v>759</v>
+      </c>
+      <c r="D109" t="s">
+        <v>247</v>
+      </c>
+      <c r="E109" t="s">
+        <v>760</v>
+      </c>
+      <c r="F109" t="s">
+        <v>262</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>762</v>
+      </c>
+      <c r="B110" t="s">
+        <v>763</v>
+      </c>
+      <c r="C110" t="s">
+        <v>246</v>
+      </c>
+      <c r="D110" t="s">
+        <v>247</v>
+      </c>
+      <c r="E110" t="s">
+        <v>764</v>
+      </c>
+      <c r="F110" t="s">
+        <v>765</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>767</v>
+      </c>
+      <c r="B111" t="s">
+        <v>768</v>
+      </c>
+      <c r="C111" t="s">
+        <v>769</v>
+      </c>
+      <c r="D111" t="s">
+        <v>247</v>
+      </c>
+      <c r="E111" t="s">
+        <v>770</v>
+      </c>
+      <c r="F111" t="s">
+        <v>262</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>772</v>
+      </c>
+      <c r="B112" t="s">
+        <v>768</v>
+      </c>
+      <c r="C112" t="s">
+        <v>253</v>
+      </c>
+      <c r="D112" t="s">
+        <v>247</v>
+      </c>
+      <c r="E112" t="s">
+        <v>770</v>
+      </c>
+      <c r="F112" t="s">
+        <v>262</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>774</v>
+      </c>
+      <c r="B113" t="s">
+        <v>775</v>
+      </c>
+      <c r="C113" t="s">
+        <v>332</v>
+      </c>
+      <c r="D113" t="s">
+        <v>247</v>
+      </c>
+      <c r="E113" t="s">
+        <v>776</v>
+      </c>
+      <c r="F113" t="s">
+        <v>777</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>779</v>
+      </c>
+      <c r="B114" t="s">
+        <v>780</v>
+      </c>
+      <c r="C114" t="s">
+        <v>246</v>
+      </c>
+      <c r="D114" t="s">
+        <v>254</v>
+      </c>
+      <c r="E114" t="s">
+        <v>781</v>
+      </c>
+      <c r="F114" t="s">
+        <v>544</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>783</v>
+      </c>
+      <c r="B115" t="s">
+        <v>784</v>
+      </c>
+      <c r="C115" t="s">
+        <v>205</v>
+      </c>
+      <c r="D115" t="s">
+        <v>247</v>
+      </c>
+      <c r="E115" t="s">
+        <v>785</v>
+      </c>
+      <c r="F115" t="s">
+        <v>786</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>788</v>
+      </c>
+      <c r="B116" t="s">
+        <v>789</v>
+      </c>
+      <c r="C116" t="s">
+        <v>790</v>
+      </c>
+      <c r="D116" t="s">
+        <v>247</v>
+      </c>
+      <c r="E116" t="s">
+        <v>791</v>
+      </c>
+      <c r="F116" t="s">
+        <v>792</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>794</v>
+      </c>
+      <c r="B117" t="s">
+        <v>795</v>
+      </c>
+      <c r="C117" t="s">
+        <v>664</v>
+      </c>
+      <c r="D117" t="s">
+        <v>568</v>
+      </c>
+      <c r="E117" t="s">
+        <v>796</v>
+      </c>
+      <c r="F117" t="s">
+        <v>693</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>798</v>
+      </c>
+      <c r="B118" t="s">
+        <v>799</v>
+      </c>
+      <c r="C118" t="s">
+        <v>246</v>
+      </c>
+      <c r="D118" t="s">
+        <v>247</v>
+      </c>
+      <c r="E118" t="s">
+        <v>800</v>
+      </c>
+      <c r="F118" t="s">
+        <v>801</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>803</v>
+      </c>
+      <c r="B119" t="s">
+        <v>804</v>
+      </c>
+      <c r="C119" t="s">
+        <v>805</v>
+      </c>
+      <c r="D119" t="s">
+        <v>247</v>
+      </c>
+      <c r="E119" t="s">
+        <v>806</v>
+      </c>
+      <c r="F119" t="s">
+        <v>256</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>808</v>
+      </c>
+      <c r="B120" t="s">
+        <v>809</v>
+      </c>
+      <c r="C120" t="s">
+        <v>246</v>
+      </c>
+      <c r="D120" t="s">
+        <v>247</v>
+      </c>
+      <c r="E120" t="s">
+        <v>810</v>
+      </c>
+      <c r="F120" t="s">
+        <v>359</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>812</v>
+      </c>
+      <c r="B121" t="s">
+        <v>813</v>
+      </c>
+      <c r="C121" t="s">
+        <v>814</v>
+      </c>
+      <c r="D121" t="s">
+        <v>351</v>
+      </c>
+      <c r="E121" t="s">
+        <v>815</v>
+      </c>
+      <c r="F121" t="s">
+        <v>816</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>818</v>
+      </c>
+      <c r="B122" t="s">
+        <v>819</v>
+      </c>
+      <c r="C122" t="s">
+        <v>332</v>
+      </c>
+      <c r="D122" t="s">
+        <v>247</v>
+      </c>
+      <c r="E122" t="s">
+        <v>820</v>
+      </c>
+      <c r="F122" t="s">
+        <v>821</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>823</v>
+      </c>
+      <c r="B123" t="s">
+        <v>824</v>
+      </c>
+      <c r="C123" t="s">
+        <v>825</v>
+      </c>
+      <c r="D123" t="s">
+        <v>247</v>
+      </c>
+      <c r="E123" t="s">
+        <v>262</v>
+      </c>
+      <c r="F123" t="s">
+        <v>826</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>823</v>
+      </c>
+      <c r="B124" t="s">
+        <v>824</v>
+      </c>
+      <c r="C124" t="s">
+        <v>825</v>
+      </c>
+      <c r="D124" t="s">
+        <v>254</v>
+      </c>
+      <c r="E124" t="s">
+        <v>262</v>
+      </c>
+      <c r="F124" t="s">
+        <v>828</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>829</v>
       </c>
     </row>
   </sheetData>
@@ -5027,6 +6940,55 @@
     <hyperlink ref="H73" r:id="rId72"/>
     <hyperlink ref="H74" r:id="rId73"/>
     <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-09-23.xlsx
+++ b/docs/xlsx/jobs-2026-09-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="839">
   <si>
     <t>Title</t>
   </si>
@@ -748,6 +748,30 @@
     <t>https://www.conservationjobboard.com/job-listing-work-planner-muskegon-michigan/8154284012</t>
   </si>
   <si>
+    <t>Regional Campaign Manager, Southwest</t>
+  </si>
+  <si>
+    <t>Greenlight America</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Clean Energy</t>
+  </si>
+  <si>
+    <t>Idealist</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/regional-campaign-manager-southwest-2/</t>
+  </si>
+  <si>
     <t>Accounting Manager</t>
   </si>
   <si>
@@ -802,9 +826,6 @@
     <t>USD 52000.00 - 57000.00/year</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/consultant-job/e1bac9e9b9834258ae687e4a2cb676ae-administrative-assistantparalegal-terris-pravlik-millian-llp-washington</t>
   </si>
   <si>
@@ -1012,9 +1033,6 @@
     <t>Parkinson's Foundation</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>USD 65000.00 - 75000.00/year</t>
   </si>
   <si>
@@ -2164,19 +2182,22 @@
     <t>https://www.idealist.org/en/nonprofit-job/3487ab37030e4ca59d8bc97e2eb5fa30-rape-crisis-advocate-training-curriculum-consultant-new-york-city-alliance-against-sexual-assault-new-york</t>
   </si>
   <si>
+    <t>The Alliance Against Sexual Violence</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3487ab37030e4ca59d8bc97e2eb5fa30-rape-crisis-advocate-training-curriculum-consultant-the-alliance-against-sexual-violence-new-york</t>
+  </si>
+  <si>
     <t>Regional Campaign Manager, NY &amp; NJ</t>
   </si>
   <si>
-    <t>Greenlight America</t>
-  </si>
-  <si>
     <t>Climate Change, Energy</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/37ce7bb2441541ac9106a1e4e968e21c-regional-campaign-manager-ny-nj-greenlight-america-washington</t>
   </si>
   <si>
-    <t>Regional Campaign Manager, Southwest</t>
+    <t>Green Jobs</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/e58f5e30d0094cd581f5c8628d2ee6c6-regional-campaign-manager-southwest-greenlight-america-washington</t>
@@ -2468,6 +2489,12 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/cf5c33341579428c9af09fa39ec52583-temporary-bilingual-test-administrator-university-of-chicago-health-lab-coachella</t>
+  </si>
+  <si>
+    <t>Harris School of Public Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf5c33341579428c9af09fa39ec52583-temporary-bilingual-test-administrator-harris-school-of-public-policy-coachella</t>
   </si>
   <si>
     <t>Vice President of Corporate Partnerships</t>
@@ -3947,7 +3974,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3986,8 +4013,37 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F2" t="s">
+        <v>249</v>
+      </c>
+      <c r="G2" t="s">
+        <v>250</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3995,7 +4051,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -4036,2233 +4092,2233 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E2" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B3" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D3" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E3" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="F3" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="B4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D4" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E4" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="F4" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B5" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C5" t="s">
         <v>235</v>
       </c>
       <c r="D5" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E5" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="F5" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B6" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C6" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D6" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E6" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F6" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B7" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C7" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D7" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E7" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="F7" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B8" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="C8" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D8" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E8" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="F8" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B9" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C9" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D9" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E9" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F9" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="B10" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="C10" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D10" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E10" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="F10" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B11" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C11" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="D11" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E11" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F11" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B12" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C12" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="D12" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E12" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F12" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B13" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C13" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="D13" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E13" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F13" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B14" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C14" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="D14" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E14" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F14" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B15" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C15" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="D15" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E15" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="F15" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B16" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C16" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="D16" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E16" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="F16" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B17" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C17" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="D17" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E17" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F17" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B18" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="C18" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D18" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E18" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="F18" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B19" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C19" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="D19" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E19" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="F19" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B20" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C20" t="s">
-        <v>332</v>
+        <v>246</v>
       </c>
       <c r="D20" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E20" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F20" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B21" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C21" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D21" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E21" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="F21" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B22" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C22" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="D22" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E22" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="F22" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B23" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C23" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D23" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E23" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="F23" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B24" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C24" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="D24" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E24" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F24" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B25" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C25" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D25" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E25" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F25" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B26" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="C26" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="D26" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E26" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F26" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B27" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C27" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D27" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E27" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="F27" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B28" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C28" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D28" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E28" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="F28" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B29" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C29" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D29" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E29" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="F29" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B30" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C30" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="D30" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E30" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="F30" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B31" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C31" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D31" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E31" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="F31" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B32" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C32" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="D32" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E32" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="F32" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="B33" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C33" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="D33" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E33" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="F33" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B34" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C34" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="D34" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E34" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="F34" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B35" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C35" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="D35" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E35" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="F35" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B36" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C36" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="D36" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E36" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="F36" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="B37" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C37" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D37" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E37" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="F37" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="B38" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C38" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D38" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E38" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F38" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B39" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C39" t="s">
-        <v>332</v>
+        <v>246</v>
       </c>
       <c r="D39" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E39" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="F39" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="B40" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C40" t="s">
-        <v>332</v>
+        <v>246</v>
       </c>
       <c r="D40" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E40" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="F40" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B41" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="C41" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D41" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E41" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="F41" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="B42" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C42" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D42" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E42" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="F42" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B43" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C43" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D43" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E43" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F43" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="B44" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="C44" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D44" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E44" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="F44" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B45" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="C45" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="D45" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E45" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F45" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B46" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C46" t="s">
-        <v>332</v>
+        <v>246</v>
       </c>
       <c r="D46" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E46" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F46" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B47" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C47" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="D47" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E47" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F47" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B48" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C48" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D48" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E48" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F48" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="B49" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="C49" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="D49" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E49" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="F49" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="B50" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="C50" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="D50" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E50" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="F50" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="B51" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C51" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D51" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E51" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="F51" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="B52" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C52" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D52" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E52" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F52" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B53" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C53" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D53" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E53" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="F53" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="B54" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="C54" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="D54" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E54" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="F54" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B55" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C55" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D55" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E55" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="F55" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B56" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C56" t="s">
-        <v>332</v>
+        <v>246</v>
       </c>
       <c r="D56" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E56" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="F56" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="B57" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C57" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D57" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E57" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="F57" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B58" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="C58" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="D58" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E58" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="F58" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="B59" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="C59" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D59" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E59" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="F59" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="B60" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="C60" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D60" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E60" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="F60" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="B61" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="C61" t="s">
-        <v>332</v>
+        <v>246</v>
       </c>
       <c r="D61" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E61" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="F61" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="B62" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C62" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D62" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E62" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="F62" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="B63" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="C63" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="D63" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E63" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="F63" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="B64" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="C64" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D64" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E64" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="F64" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="B65" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C65" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="D65" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E65" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="F65" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B66" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="C66" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D66" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="E66" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="F66" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B67" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="C67" t="s">
-        <v>332</v>
+        <v>246</v>
       </c>
       <c r="D67" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E67" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="F67" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="B68" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="C68" t="s">
         <v>164</v>
       </c>
       <c r="D68" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E68" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="F68" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B69" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="C69" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="D69" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E69" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="F69" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B70" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="C70" t="s">
-        <v>332</v>
+        <v>246</v>
       </c>
       <c r="D70" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E70" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="F70" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B71" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C71" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="D71" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E71" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F71" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B72" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C72" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D72" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E72" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F72" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B73" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C73" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="D73" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E73" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F73" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B74" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C74" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="D74" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E74" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F74" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B75" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C75" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="D75" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E75" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F75" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B76" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C76" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="D76" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E76" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F76" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="B77" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="C77" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="D77" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E77" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="F77" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="B78" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="C78" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="D78" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E78" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="F78" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="B79" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="C79" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="D79" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E79" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="F79" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="B80" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="C80" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="D80" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E80" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="F80" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="B81" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="C81" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="D81" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E81" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F81" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="B82" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C82" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D82" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E82" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="F82" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="B83" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="C83" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="D83" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="E83" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="F83" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="B84" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="C84" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="D84" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E84" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="F84" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B85" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="C85" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D85" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E85" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="F85" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="B86" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="C86" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D86" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E86" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="F86" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="B87" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="C87" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D87" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E87" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="F87" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="B88" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="C88" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="D88" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E88" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="F88" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="B89" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="C89" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D89" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E89" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="F89" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="B90" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="C90" t="s">
-        <v>332</v>
+        <v>246</v>
       </c>
       <c r="D90" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E90" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="F90" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="B91" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="C91" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="D91" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E91" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="F91" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="B92" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="C92" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D92" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E92" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="F92" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="B93" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="C93" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D93" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E93" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F93" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="B94" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="C94" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D94" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E94" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="F94" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="B95" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="C95" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="D95" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E95" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F95" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="B96" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="C96" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="D96" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E96" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F96" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="B97" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="C97" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="D97" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E97" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="F97" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="B98" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="C98" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="D98" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E98" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="F98" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -6270,597 +6326,646 @@
         <v>716</v>
       </c>
       <c r="B99" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="C99" t="s">
-        <v>332</v>
+        <v>718</v>
       </c>
       <c r="D99" t="s">
-        <v>247</v>
+        <v>524</v>
       </c>
       <c r="E99" t="s">
-        <v>473</v>
+        <v>719</v>
       </c>
       <c r="F99" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B100" t="s">
-        <v>717</v>
+        <v>245</v>
       </c>
       <c r="C100" t="s">
-        <v>332</v>
+        <v>246</v>
       </c>
       <c r="D100" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E100" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F100" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>722</v>
+        <v>244</v>
       </c>
       <c r="B101" t="s">
-        <v>683</v>
+        <v>245</v>
       </c>
       <c r="C101" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="D101" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E101" t="s">
-        <v>723</v>
+        <v>479</v>
       </c>
       <c r="F101" t="s">
-        <v>262</v>
+        <v>725</v>
+      </c>
+      <c r="G101" t="s">
+        <v>727</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="B102" t="s">
-        <v>726</v>
+        <v>689</v>
       </c>
       <c r="C102" t="s">
-        <v>727</v>
+        <v>268</v>
       </c>
       <c r="D102" t="s">
-        <v>518</v>
+        <v>255</v>
       </c>
       <c r="E102" t="s">
-        <v>262</v>
+        <v>730</v>
       </c>
       <c r="F102" t="s">
-        <v>728</v>
+        <v>248</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B103" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C103" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D103" t="s">
-        <v>351</v>
+        <v>524</v>
       </c>
       <c r="E103" t="s">
-        <v>733</v>
+        <v>248</v>
       </c>
       <c r="F103" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B104" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C104" t="s">
-        <v>477</v>
+        <v>739</v>
       </c>
       <c r="D104" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E104" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="F104" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B105" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C105" t="s">
-        <v>332</v>
+        <v>483</v>
       </c>
       <c r="D105" t="s">
-        <v>247</v>
+        <v>357</v>
       </c>
       <c r="E105" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="F105" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B106" t="s">
-        <v>663</v>
+        <v>749</v>
       </c>
       <c r="C106" t="s">
-        <v>664</v>
+        <v>246</v>
       </c>
       <c r="D106" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E106" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="F106" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="B107" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="C107" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="D107" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="E107" t="s">
-        <v>370</v>
+        <v>754</v>
       </c>
       <c r="F107" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="B108" t="s">
-        <v>753</v>
+        <v>669</v>
       </c>
       <c r="C108" t="s">
-        <v>754</v>
+        <v>670</v>
       </c>
       <c r="D108" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E108" t="s">
+        <v>376</v>
+      </c>
+      <c r="F108" t="s">
         <v>755</v>
       </c>
-      <c r="F108" t="s">
-        <v>756</v>
-      </c>
       <c r="H108" s="2" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B109" t="s">
-        <v>683</v>
+        <v>760</v>
       </c>
       <c r="C109" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D109" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E109" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="F109" t="s">
-        <v>262</v>
+        <v>763</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="B110" t="s">
-        <v>763</v>
+        <v>689</v>
       </c>
       <c r="C110" t="s">
-        <v>246</v>
+        <v>766</v>
       </c>
       <c r="D110" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E110" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="F110" t="s">
-        <v>765</v>
+        <v>248</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B111" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C111" t="s">
-        <v>769</v>
+        <v>254</v>
       </c>
       <c r="D111" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E111" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F111" t="s">
-        <v>262</v>
+        <v>772</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B112" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="C112" t="s">
-        <v>253</v>
+        <v>776</v>
       </c>
       <c r="D112" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E112" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="F112" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="B113" t="s">
         <v>775</v>
       </c>
       <c r="C113" t="s">
-        <v>332</v>
+        <v>261</v>
       </c>
       <c r="D113" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E113" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F113" t="s">
-        <v>777</v>
+        <v>248</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B114" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C114" t="s">
         <v>246</v>
       </c>
       <c r="D114" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E114" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="F114" t="s">
-        <v>544</v>
+        <v>784</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B115" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="C115" t="s">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="D115" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="E115" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="F115" t="s">
-        <v>786</v>
+        <v>550</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B116" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C116" t="s">
-        <v>790</v>
+        <v>205</v>
       </c>
       <c r="D116" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E116" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="F116" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B117" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C117" t="s">
-        <v>664</v>
+        <v>797</v>
       </c>
       <c r="D117" t="s">
-        <v>568</v>
+        <v>255</v>
       </c>
       <c r="E117" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="F117" t="s">
-        <v>693</v>
+        <v>799</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="B118" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C118" t="s">
-        <v>246</v>
+        <v>670</v>
       </c>
       <c r="D118" t="s">
-        <v>247</v>
+        <v>574</v>
       </c>
       <c r="E118" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="F118" t="s">
-        <v>801</v>
+        <v>699</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B119" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C119" t="s">
-        <v>805</v>
+        <v>254</v>
       </c>
       <c r="D119" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E119" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="F119" t="s">
-        <v>256</v>
+        <v>808</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B120" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C120" t="s">
-        <v>246</v>
+        <v>812</v>
       </c>
       <c r="D120" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E120" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="F120" t="s">
-        <v>359</v>
+        <v>264</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="B121" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C121" t="s">
-        <v>814</v>
+        <v>254</v>
       </c>
       <c r="D121" t="s">
-        <v>351</v>
+        <v>255</v>
       </c>
       <c r="E121" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="F121" t="s">
-        <v>816</v>
+        <v>365</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B122" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C122" t="s">
-        <v>332</v>
+        <v>821</v>
       </c>
       <c r="D122" t="s">
-        <v>247</v>
+        <v>357</v>
       </c>
       <c r="E122" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="F122" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>819</v>
+      </c>
+      <c r="B123" t="s">
+        <v>825</v>
+      </c>
+      <c r="C123" t="s">
+        <v>821</v>
+      </c>
+      <c r="D123" t="s">
+        <v>357</v>
+      </c>
+      <c r="E123" t="s">
+        <v>822</v>
+      </c>
+      <c r="F123" t="s">
         <v>823</v>
       </c>
-      <c r="B123" t="s">
-        <v>824</v>
-      </c>
-      <c r="C123" t="s">
-        <v>825</v>
-      </c>
-      <c r="D123" t="s">
-        <v>247</v>
-      </c>
-      <c r="E123" t="s">
-        <v>262</v>
-      </c>
-      <c r="F123" t="s">
+      <c r="H123" s="2" t="s">
         <v>826</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="B124" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="C124" t="s">
-        <v>825</v>
+        <v>246</v>
       </c>
       <c r="D124" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E124" t="s">
+        <v>829</v>
+      </c>
+      <c r="F124" t="s">
+        <v>830</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>832</v>
+      </c>
+      <c r="B125" t="s">
+        <v>833</v>
+      </c>
+      <c r="C125" t="s">
+        <v>834</v>
+      </c>
+      <c r="D125" t="s">
+        <v>255</v>
+      </c>
+      <c r="E125" t="s">
+        <v>248</v>
+      </c>
+      <c r="F125" t="s">
+        <v>835</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>832</v>
+      </c>
+      <c r="B126" t="s">
+        <v>833</v>
+      </c>
+      <c r="C126" t="s">
+        <v>834</v>
+      </c>
+      <c r="D126" t="s">
         <v>262</v>
       </c>
-      <c r="F124" t="s">
-        <v>828</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>829</v>
+      <c r="E126" t="s">
+        <v>248</v>
+      </c>
+      <c r="F126" t="s">
+        <v>837</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>838</v>
       </c>
     </row>
   </sheetData>
@@ -6989,6 +7094,8 @@
     <hyperlink ref="H122" r:id="rId121"/>
     <hyperlink ref="H123" r:id="rId122"/>
     <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
